--- a/FAO_Lebanon.xlsx
+++ b/FAO_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2622,6 +2622,2166 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, FAO and WFP Celebrate World Food Day 2026 in Baadaran, Chouf Highlighting Innovation for Sustainable Food Systems</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/ministry-of-agriculture--fao-and-wfp-celebrate-world-food-day-2026-in-baadaran--chouf-highlighting-innovation-for-sustainable-food-systems/en</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, FAO and WFP Celebrate World Food Day 2026 in Baadaran, Chouf Highlighting Innovation for Sustainable Food Systems
+The Ministry of Agriculture, the Food and Agriculture Organization of the United Nations (FAO) and the World Food Programme (WFP) together with Baadaran municipality and Shouf Reserve celebrated World Food Day 2026 in Baadaran, Chouf, under the theme “Innovate today. Nourish tomorrow.” The event was held under the patronage and in the presence of H.E. Dr Nizar Hani, Minister of Agriculture, bringing together representatives of diplomatic missions, public institutions, international organizations, municipalities, agricultural unions and cooperatives, as well as farmers, food producers and rural development partners.
+Hosted at Beit el Dayaa, the celebration brought agricultural innovation and local food heritage together, providing a platform to exchange knowledge, showcase practical solutions and strengthen partnerships that support agricultural production and rural livelihoods. Discussions highlighted how knowledge, technology and collaboration can help farmers improve their incomes, protect natural resources and create opportunities for women and young people.
+World Food Day is celebrated every year on 16 October to mark the founding of FAO in 1945. In 2026, the global theme “Innovate today. Nourish tomorrow.” calls for innovation and collective action to help build a more sustainable food-secure future for all.
+The opening ceremony featured remarks by Mr Walid Khattar, Head of Baadaran Municipality; Eng. Louis Lahoud, Director-General of the Ministry of Agriculture; Ms Allison Oman Lawi, WFP Representative and Country Director in Lebanon; Ms Veronica Quattrola, FAO Representative in Lebanon; and Minister Hani.
+Minister of Agriculture Nizar Hani reaffirmed the importance of securing access to adequate, healthy and safe food while protecting the land and natural resources on which food production depends. He stressed that revitalizing rural areas requires creating employment opportunities, increasing the value of local production and enabling people to build their futures in their villages.
+“The future of rural areas is built when people find opportunities to work on their land, value in their production, and reasons to stay and build a life in their villages,” Hani said.
+The Minister also highlighted the need to link immediate assistance with sustainable investment that strengthens local production, improves nutrition and creates jobs. He emphasized that partnerships must translate into measurable results in the field, including higher productivity, lower production costs and more stable incomes for farmers.
+Addressing the challenges facing agricultural communities in southern Lebanon, Hani stressed the importance of assessing damage, restoring productive infrastructure, rehabilitating irrigation systems, protecting soil and helping farmers resume agricultural seasons. He also highlighted the role of innovation in addressing everyday farming challenges, from using water more efficiently and detecting pests early to reducing food loss and improving product traceability and safety.
+In her remarks, FAO Representative in Lebanon Veronica Quattrola emphasized that innovation is not limited to advanced machinery or artificial intelligence. It can also mean finding better ways to use water, bringing young people’s ideas into agriculture, or turning a family recipe into a source of income.
+“We must listen before offering solutions and involve farmers, both women and men, in the decisions that affect their lives and work,” Quattrola stressed, highlighting the importance of building on farmers’ knowledge and experience when introducing new technologies.
+She noted that innovation must deliver tangible results: helping farmers continue working their land, enabling families to sustain their livelihoods and giving rural communities greater confidence in planning for the future.
+Quattrola also highlighted FAO’s work in Lebanon to improve agricultural production, develop rural enterprises, facilitate market access, promote the sustainable management of land, water and forests, and strengthen adaptation to climate change. She underscored the importance of the partnership with the Ministry of Agriculture and of bringing together farmers, universities, researchers, public institutions and the private sector to scale up solutions that benefit more producers.
+WFP Representative and Country Director in Lebanon Allison Oman Lawi highlighted the continuing pressures on Lebanese households, farmers and communities following years of overlapping crises. She stressed that food security depends not only on access to nutritious food, but also on addressing high production costs and helping families restore their livelihoods.
+Lawi noted that innovation includes making better use of resources, knowledge and partnerships, helping farmers adapt to changing circumstances, connecting producers with new opportunities and strengthening national systems that support access to food. She reaffirmed WFP’s commitment, under the leadership of the Lebanese Government and in collaboration with partners, to supporting vulnerable households while strengthening food systems and national institutional capacities.
+The event also featured practical activities showcasing how innovation can connect scientific knowledge with local expertise. An agricultural innovation exhibition presented solutions and approaches relevant to agricultural production, while a panel discussion entitled “Success Stories: Innovation in Agriculture and Food Production” was moderated by Dr Nadine Nassif, Dean of the Faculty of Agriculture at the Lebanese University.
+An interactive presentation by Debbane Group explored “Artificial Intelligence and Digital Transformation in Agriculture,” highlighting the potential of emerging technologies to improve agricultural practices and production.
+The programme concluded with an exhibition of local food products and traditional Lebanese preserves, accompanied by a rural lunch, celebrating the region’s food heritage and demonstrating opportunities to connect farming with food processing, marketing and rural tourism.
+By bringing together farmers, public institutions, international organizations, researchers and local communities, the World Food Day celebration in Baadaran highlighted the importance of making innovation practical, inclusive and accessible. Strengthening these partnerships can help farmers and food producers improve productivity and incomes, protect natural resources and contribute to more resilient food systems in Lebanon.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:40:30.704001+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, FAO and WFP Celebrate World Food Day 2026 in Baadaran, Chouf Highlighting Innovation for Sustainable Food Systems</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.fao.org:443/lebanon/news/detail/ministry-of-agriculture--fao-and-wfp-celebrate-world-food-day-2026-in-baadaran--chouf-highlighting-innovation-for-sustainable-food-systems/en</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, FAO and WFP Celebrate World Food Day 2026 in Baadaran, Chouf Highlighting Innovation for Sustainable Food Systems
+The Ministry of Agriculture, the Food and Agriculture Organization of the United Nations (FAO) and the World Food Programme (WFP) together with Baadaran municipality and Shouf Reserve celebrated World Food Day 2026 in Baadaran, Chouf, under the theme “Innovate today. Nourish tomorrow.” The event was held under the patronage and in the presence of H.E. Dr Nizar Hani, Minister of Agriculture, bringing together representatives of diplomatic missions, public institutions, international organizations, municipalities, agricultural unions and cooperatives, as well as farmers, food producers and rural development partners.
+Hosted at Beit el Dayaa, the celebration brought agricultural innovation and local food heritage together, providing a platform to exchange knowledge, showcase practical solutions and strengthen partnerships that support agricultural production and rural livelihoods. Discussions highlighted how knowledge, technology and collaboration can help farmers improve their incomes, protect natural resources and create opportunities for women and young people.
+World Food Day is celebrated every year on 16 October to mark the founding of FAO in 1945. In 2026, the global theme “Innovate today. Nourish tomorrow.” calls for innovation and collective action to help build a more sustainable food-secure future for all.
+The opening ceremony featured remarks by Mr Walid Khattar, Head of Baadaran Municipality; Eng. Louis Lahoud, Director-General of the Ministry of Agriculture; Ms Allison Oman Lawi, WFP Representative and Country Director in Lebanon; Ms Veronica Quattrola, FAO Representative in Lebanon; and Minister Hani.
+Minister of Agriculture Nizar Hani reaffirmed the importance of securing access to adequate, healthy and safe food while protecting the land and natural resources on which food production depends. He stressed that revitalizing rural areas requires creating employment opportunities, increasing the value of local production and enabling people to build their futures in their villages.
+“The future of rural areas is built when people find opportunities to work on their land, value in their production, and reasons to stay and build a life in their villages,” Hani said.
+The Minister also highlighted the need to link immediate assistance with sustainable investment that strengthens local production, improves nutrition and creates jobs. He emphasized that partnerships must translate into measurable results in the field, including higher productivity, lower production costs and more stable incomes for farmers.
+Addressing the challenges facing agricultural communities in southern Lebanon, Hani stressed the importance of assessing damage, restoring productive infrastructure, rehabilitating irrigation systems, protecting soil and helping farmers resume agricultural seasons. He also highlighted the role of innovation in addressing everyday farming challenges, from using water more efficiently and detecting pests early to reducing food loss and improving product traceability and safety.
+In her remarks, FAO Representative in Lebanon Veronica Quattrola emphasized that innovation is not limited to advanced machinery or artificial intelligence. It can also mean finding better ways to use water, bringing young people’s ideas into agriculture, or turning a family recipe into a source of income.
+“We must listen before offering solutions and involve farmers, both women and men, in the decisions that affect their lives and work,” Quattrola stressed, highlighting the importance of building on farmers’ knowledge and experience when introducing new technologies.
+She noted that innovation must deliver tangible results: helping farmers continue working their land, enabling families to sustain their livelihoods and giving rural communities greater confidence in planning for the future.
+Quattrola also highlighted FAO’s work in Lebanon to improve agricultural production, develop rural enterprises, facilitate market access, promote the sustainable management of land, water and forests, and strengthen adaptation to climate change. She underscored the importance of the partnership with the Ministry of Agriculture and of bringing together farmers, universities, researchers, public institutions and the private sector to scale up solutions that benefit more producers.
+WFP Representative and Country Director in Lebanon Allison Oman Lawi highlighted the continuing pressures on Lebanese households, farmers and communities following years of overlapping crises. She stressed that food security depends not only on access to nutritious food, but also on addressing high production costs and helping families restore their livelihoods.
+Lawi noted that innovation includes making better use of resources, knowledge and partnerships, helping farmers adapt to changing circumstances, connecting producers with new opportunities and strengthening national systems that support access to food. She reaffirmed WFP’s commitment, under the leadership of the Lebanese Government and in collaboration with partners, to supporting vulnerable households while strengthening food systems and national institutional capacities.
+The event also featured practical activities showcasing how innovation can connect scientific knowledge with local expertise. An agricultural innovation exhibition presented solutions and approaches relevant to agricultural production, while a panel discussion entitled “Success Stories: Innovation in Agriculture and Food Production” was moderated by Dr Nadine Nassif, Dean of the Faculty of Agriculture at the Lebanese University.
+An interactive presentation by Debbane Group explored “Artificial Intelligence and Digital Transformation in Agriculture,” highlighting the potential of emerging technologies to improve agricultural practices and production.
+The programme concluded with an exhibition of local food products and traditional Lebanese preserves, accompanied by a rural lunch, celebrating the region’s food heritage and demonstrating opportunities to connect farming with food processing, marketing and rural tourism.
+By bringing together farmers, public institutions, international organizations, researchers and local communities, the World Food Day celebration in Baadaran highlighted the importance of making innovation practical, inclusive and accessible. Strengthening these partnerships can help farmers and food producers improve productivity and incomes, protect natural resources and contribute to more resilient food systems in Lebanon.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:40:36.606058+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture and FAO Provide Urgent Cash Support to Livestock Farmers Affected by Conflict in South Lebanon</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.fao.org:443/lebanon/news/detail/ministry-of-agriculture-and-fao-provide-urgent-cash-support-to-livestock-farmers-affected-by-conflict-in-south-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture and FAO Provide Urgent Cash Support to Livestock Farmers Affected by Conflict in South Lebanon
+©FAO Lebanon/ Ralph Azar
+The Ministry of Agriculture, in collaboration with the Food and Agriculture Organization of the United Nations (FAO), has launched a targeted cash assistance intervention to support dairy livestock farmers affected by the hostilities in South Lebanon and Nabatieh Governorates. The initiative will reach 465 vulnerable farmers with a total value of about USD 140 thousand.
+The dairy livestock sector in Lebanon, which sustains more than 13 000 farms, is facing mounting pressure due to long-standing structural challenges, including limited veterinary services and the high cost of fodder. These challenges have been further exacerbated by the recent conflict.
+To address the most urgent needs, the Ministry of Agriculture and FAO will provide unconditional cash transfers to livestock farmers in conflict-affected areas of South Lebanon. Each beneficiary will receive USD 300 to support essential livestock-related expenses, including animal feed, veterinary care, and other inputs required to sustain production.
+The intervention targets active Lebanese small- scale livestock keepers engaged in the dairy value chain, particularly those who own large ruminants currently in production and who have been directly impacted by the recent developments.
+Nizar Hani, Lebanon’s Minister of Agriculture, stated: “Supporting livestock breeders in South Lebanon and Nabatieh goes beyond an emergency response to the current crisis; it constitutes a fundamental pillar in safeguarding national food security and ensuring the continuity of agricultural and livestock production in the rural areas most severely affected. The livestock sector represents an economic and social lifeline for thousands of Lebanese families, and any decline in this sector directly impacts the food and livelihood security of local communities.”
+He added: “This joint initiative with the Food and Agriculture Organization of the United Nations is part of an integrated scientific and humanitarian approach adopted by the Ministry of Agriculture, aimed at strengthening farmers’ resilience and securing the minimum conditions necessary for continuity and productivity, particularly amid the compounded challenges resulting from conflicts, economic hardship, and climate-related pressures. We reaffirm the Ministry’s commitment to continuing cooperation with international partners and local institutions to develop sustainable support programmes for the agricultural and livestock sectors. These efforts are centred on protecting rural livelihoods, improving veterinary services, and enhancing local production capacities, thereby contributing to the development of a more resilient and sustainable agricultural sector capable of adapting to crises.”
+Minister Hani also expressed his appreciation to the Lebanese Armed Forces and the UNIFIL for their efforts in assisting with the relocation of farms and livestock to safer areas, helping to reduce losses and protect the livelihoods of farmers in the affected regions.
+“Livestock farmers are central to Lebanon’s food security, yet the ongoing crisis is placing their animals, livelihoods and capacity to produce food under increasing pressure,” said FAO Representative in Lebanon, Veronica Quattrola. “Through this cash assistance, FAO and the Ministry of Agriculture are providing timely and flexible support to help farmers meet urgent needs, safeguard their productive assets and maintain the supply of essential dairy products to local markets—strengthening national food security and the resilience of rural communities.”
+This intervention forms part of FAO’s ongoing efforts, in close collaboration with the Ministry of Agriculture, to respond to the immediate impacts of the crisis while strengthening the resilience of Lebanon’s agrifood systems and safeguarding rural livelihoods in conflict-affected areas.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:40:43.172916+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FAO high-level mission to Lebanon begins with focus on partnership, food security and resilience</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/fao-high-level-mission-to-lebanon-begins-with-focus-on-partnership--food-security-and-resilience/en</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FAO high-level mission to Lebanon begins with focus on partnership, food security and resilience
+A high-level delegation from the Food and Agriculture Organization of the United Nations (FAO) began a four-day mission to Lebanon, from 30 September to 3 October, to deepen partnerships and advance joint efforts in support of Lebanon’s agricultural and food systems, resilience and sustainable development.
+The delegation is led by FAO Deputy Director-General Beth Bechdol, alongside AbdulHakim Elwaer, FAO Assistant Director-General and Regional Representative for the Near East and North Africa, and Rein Paulsen, Director of FAO’s Office of Emergencies and Resilience (OER). Veronica Quattrola, newly appointed FAO Representative in Lebanon, is also joining the mission.
+On the first day, the delegation met with key international partners to discuss common priorities and ways to support Lebanon’s agricultural sector and rural communities.
+During a meeting with Kenji Yokota, Ambassador of Japan to Lebanon, the delegation recognized Japan’s longstanding support and discussed opportunities to further advance food security and support farming communities.
+Discussions with Alessandra Viezzer, Head of Cooperation at the European Union Delegation to Lebanon, and the EU team focused on priorities for Lebanon’s agricultural sector, with particular attention to resilience and sustainable development.
+The delegation also met with Reidun Otterøy, Deputy Head of Mission at the Royal Norwegian Embassy in Beirut, to discuss areas including fisheries, water management and resilient livelihoods.
+As part of the day’s engagements, Rein Paulsen and Veronica Quattrola held a bilateral meeting with Kristin Knutson, Head of the United Nations Office for the Coordination of Humanitarian Affairs (OCHA) in Lebanon, focusing on improving humanitarian coordination and support for vulnerable communities, including food security and time-critical, life-saving agricultural assistance.
+The mission will continue through 3 October with meetings with senior government officials, development partners and other key stakeholders, as well as visits to rural communities and meetings with farmers to hear directly about their priorities and challenges. These engagements will provide an opportunity to exchange views on Lebanon’s evolving needs and identify opportunities for closer collaboration and coordinated action.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:40:49.660746+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FAO Lebanon welcomes Veronica Quattrola as new FAO Representative</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.fao.org:443/lebanon/news/detail/fao-lebanon-welcomes-veronica-quattrola-as-new-fao-representative/en</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>FAO Lebanon welcomes Veronica Quattrola as new FAO Representative
+Veronica Quattrola FAO Representative in Lebanon
+©FAO Lebanon
+With the agreement of the Government of the Republic of Lebanon, Ms Veronica Quattrola has been appointed Representative of the Food and Agriculture Organization of the United Nations (FAO) in Lebanon, effective 21 September 2026.
+Ms. Quattrola, an Italian national, brings extensive experience in international cooperation, programme management policy dialogue and partnership development, as well as more than 15 years of experience with FAO in Africa and the Middle East.
+She joined FAO in 2010 as a Project Coordinator in Eritrea. She subsequently served in operational and leadership positions for the Somalia programme, as Head of Operations and Deputy FAO Representative in Sudan. Since January 2020, she has served as Deputy FAO Representative in Iraq.
+Ms. Quattrola also brings valuable experience in Lebanon, having served as Officer-in-Charge of the FAO Representation from August 2024 to June 2025. In this role, she gained first-hand knowledge of the country’s agrifood sector and institutional landscape while strengthening collaboration with national authorities and development partners.
+Ms. Quattrola holds a Master’s degree in International Cooperation from Sapienza University of Rome, a Bachelor’s degree in Economics from Roma Tre University, and a Bachelor’s degree in Architecture and Interior Design from Sapienza University of Rome.
+In her new role, Ms. Quattrola will lead FAO’s work in Lebanon in close collaboration with the Government, national institutions, development and humanitarian partners, farmers and rural communities. She will support efforts to advance sustainable and resilient agrifood systems, strengthen food security and improve rural livelihoods.
+FAO Lebanon warmly welcomes Veronica Quattrola and looks forward to continuing its work with partners across the country to build a more resilient, sustainable and food-secure future for Lebanon.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:40:56.639472+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, FAO Lebanon and Canada: An Innovative Partnership on Collective Action to Promote Food Security and Support Livelihoods in Lebanon</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.fao.org:443/lebanon/news/detail/ministry-of-agriculture--fao-lebanon-and-canada--an-innovative-partnership-on-collective-action-to-promote-food-security-and-support-livelihoods-in-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, FAO Lebanon and Canada: An Innovative Partnership on Collective Action to Promote Food Security and Support Livelihoods in Lebanon
+©FAO Lebanon
+Across Lebanon, farmers and rural communities are facing pressures that are becoming increasingly difficult to navigate alone. Small-scale farmers, rural women, youth, cooperatives and producer groups are dealing with high production costs, limited access to finance, market instability, water scarcity, climate change and the cumulative effects of a multi-faceted crisis.
+Yet, in communities across the country, another response is taking shape: collective action.
+By coming together, producers can pool resources, reduce costs, access services, strengthen their bargaining power and connect more effectively to markets and institutions. But the value of collective action goes beyond its economic benefits. It can foster solidarity, rebuild trust and strengthen social cohesion in communities affected by crisis, conflict and displacement.
+Experience has shown, however, that producer organizations need more than formal registration to deliver results. They need capable leadership, sound governance, management skills, member engagement and a supportive institutional environment.
+This recognition is increasingly reflected in Lebanon’s emerging National Agriculture Strategy 2026–2035 and the FAO Country Programming Framework (CPF) 2023–2027, both of which identify cooperatives and other forms of collective action as important drivers of rural development, food security and agrifood systems transformation.
+Working closely with the General Directorate of Cooperatives (GDC), FAO in Lebanon has been contributing to positioning cooperation as a strategic partner for food security and nutrition.
+From individual interventions to collective action
+Building on this momentum, FAO Lebanon has been placing collective action at the centre of its programmatic approach, moving away from fragmented, stand-alone interventions towards a coherent and strategic pathway.
+Support to cooperatives, producer organizations, water users’ associations, fisheries groups, women-led initiatives and youth groups has been systematically integrated across the portfolio, recognizing that collective action cuts across many areas of FAO’s work, from value chains and food security to water governance, fisheries, agroforestry and rural finance.
+To support this shift, FAO Lebanon has been developing a Collective Action Vision for the Country Office, establishing a common framework, shared tools and stronger coordination across interventions.
+At the same time, FAO has been supporting the GDC in strengthening its institutional capacities and in shaping its own strategic vision, helping to lay the foundations for a stronger enabling environment for cooperatives and producer organizations.
+Together, these efforts have been linking grassroots empowerment with institutional strengthening, creating the conditions for more sustainable impact.
+“Collective action is not merely an organizational model; it is a strategic instrument for transforming Lebanon’s agrifood systems. When farmers organize effectively, they can aggregate production, reduce input and logistics costs, adopt climate-smart technologies, improve quality and traceability, strengthen their negotiating power and secure more reliable access to finance and markets. This is particularly critical for small-scale farmers, rural women and youth, who remain among the most exposed to economic shocks, water scarcity and climate-related risks,” said Minister of Agriculture Dr Nizar Hani.
+He added: “Lebanon’s National Agriculture Strategy 2026–2035 therefore places strong, transparent and professionally managed cooperatives and producer organizations at the heart of rural development. Our partnership with FAO, the Government of Canada, the General Directorate of Cooperatives and UPA Développement International is helping us move from fragmented assistance towards sustainable, value-chain-based solutions. Our objective is clear: to transform collective capacity into higher productivity, better incomes, stronger rural livelihoods and greater food and nutrition security. Building resilient agriculture means investing not only in land, water and technology, but also in people, institutions and the trust that enables them to work together.
+From strengthening groups to strengthening the system
+A flagship example of FAO’s commitment to cooperative development is its partnership with the Ministry of Agriculture and the General Directorate of Cooperatives, supported by the Government of Canada.
+Between 2019 and 2024, the programme strengthened more than 250 women-led groups across the country. A total of 265 groups received technical and business development training, while 143 groups were equipped with productive assets that enabled them to expand collective food processing activities, improve product quality and generate income.
+The programme also strengthened the institutional capacities of the General Directorate of Cooperatives, enhancing its ability to support, monitor and coordinate cooperative development nationwide.
+With funds from the Government of Canada, FAO supported the General Directorate of Cooperatives by strengthening its Management Information System, which hosts sex-disaggregated data from cooperatives for improved analysis, management and coordination.
+“In a world often divided, cooperatives remind us that true strength lies not in competition but in joining efforts. Through solidarity, trust and cooperative values we build a better world,” said Gloria Abouzeid, Director-General of Cooperatives at the Ministry of Agriculture.
+Building on these achievements and on the impact of the achieved results of the Canada-funded project, FAO continues to promote farmers’ collective action across Lebanon’s agrifood systems.
+FAO is advancing an integrated and programmatic approach to collective action to drive inclusive and sustainable agrifood systems transformation in Lebanon. This approach is structured around three core pillars: strengthening institutions and dialogue platforms; promoting climate-smart agriculture; and enhancing governance, management, and rural finance capacities.
+By embedding collective action across its programme portfolio, FAO Lebanon strengthens alignment between policy support and field-level interventions, enabling scalable and lasting impact.
+In addition, through cooperatives, producer organisations and other community-based organisations, FAO contributes to empowering rural communities to strengthen governance, increase women’s and youth participation, enhance access to services and markets, and build resilience to climate-related and economic shocks.
+A partnership built around farmers
+A key opportunity to translate this vision into action has been provided by the Enhancing Food and Nutrition Security in Lebanon (GCP/LEB/043/CAN) project, generously funded by the Government of Canada.
+Implemented, in collaboration with the Ministry of Agriculture between 2023 and 2028, the project has been promoting the adoption of gender-responsive, nutrition-sensitive and climate-smart agricultural practices, improving the performance of fruit and vegetable value chains, particularly apples and greenhouse and open-field vegetables, and strengthening the enabling environment for value chain actors, including cooperatives and producer organizations.
+But the project has also been providing a platform for a unique and innovative multi-stakeholder partnership.
+FAO, the Ministry of Agriculture, the General Directorate of Cooperatives, the Embassy of Canada and UPA DI (UPA Développement International) have been coming together around a shared objective: empowering producer organizations as key actors in agrifood systems transformation.
+“Canada is proud to partner with FAO and UPA Développement International to bring Canadian expertise and innovation to support farmers in Lebanon. By combining our strengths, we are helping farmers enhance their productivity, strengthen their livelihoods, and build resilience in the face of economic and environmental challenges,” said Sara Price, Head of Cooperation at the Embassy of Canada.
+For FAO Representative in Lebanon Nora Ourabah Haddad, the partnership brings together complementary strengths and a distinctive approach.
+“Bringing the long-standing expertise of Canada through UPA DI, with its farmer-to-farmer, peer-to-peer approach, makes this partnership so unique. By joining forces in support of women, men and young farmers in Lebanon along focused value chains, FAO, the Embassy of Canada, UPA DI, GDC and the Ministry of Agriculture build an approach that has the potential to be replicated throughout the country and the region,” she said.
+Learning from one another
+Notably, a particularly innovative feature of the partnership has been UPA DI’s peer-to-peer approach, through which producer organizations have been strengthening one another through practical exchanges, mentoring and learning-by-doing.
+Rather than relying only on traditional technical support, the approach creates opportunities for farmers and producer organizations to learn directly from one another, share practical experience and strengthen their capacities together.
+Combined with policy dialogue and institutional support to the GDC, this approach has been helping to create a more comprehensive ecosystem for collective action to flourish.
+“Farmers learn best from other farmers. Through peer-to-peer exchanges and collective action, producers share knowledge, strengthen their organizations, and develop practical solutions tailored to their realities. Our partnership with FAO, the Ministry of Agriculture, and Canada is helping create stronger producer organizations and a more resilient future for rural communities across Lebanon,” says Hugo Beauregard-Langelier, Chief Executive Officer of UPA DI.
+From partnership to lasting impact
+Together, these achievements are demonstrating how strategic partnerships can translate the benefits of collective action into tangible improvements in food security, livelihoods and resilience.
+By connecting producer organizations, cooperatives, public institutions and development partners around a shared vision, the initiative is helping lay the foundation for more inclusive, sustainable and resilient agrifood systems in Lebanon.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:03.246723+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ITALY CONTRIBUTES EUR 5 MILLION TO FAO FOR EMERGENCY LIVELIHOOD AND FOOD SECURITY SUPPORT IN CONFLICT-AFFECTED AREAS OF LEBANON</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/italy-contributes-eur-5-million-to-fao-for-emergency-livelihood-and-food-security-support-in-conflict-affected-areas-of-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ITALY CONTRIBUTES EUR 5 MILLION TO FAO FOR EMERGENCY LIVELIHOOD AND FOOD SECURITY SUPPORT IN CONFLICT-AFFECTED AREAS OF LEBANON
+©FAO
+The Government of Italy, through the Ministry of Foreign Affairs and International Cooperation, has approved a financial contribution of EUR 5 million to the Food and Agriculture Organization of the United Nations for the implementation of the programme “Emergency and Livelihood Support in the Agrifood Sector to Conflict-Affected Areas in Lebanon.”
+The contribution will support FAO’s efforts to address the growing food security and livelihood challenges resulting from the impact of the conflict and its aftermath, which have severely affected agricultural production, disrupted rural livelihoods and increased the vulnerability of farming households and displaced populations.
+According to recent assessments, conflict-related damage, displacement and restricted access to agricultural land and markets have significantly undermined the livelihoods of rural communities, particularly in southern Lebanon and other conflict-affected areas. The situation has contributed to a deterioration in food security and placed additional pressure on already vulnerable households and local economies.
+Implemented in close coordination with the Lebanese Ministry of Agriculture, the programme will provide emergency agricultural and livelihood assistance to at least 9,850 agricultural households across the governorates of South Lebanon, Nabatieh, Bekaa and Baalbek-Hermel, while engaging approximately 2,200 internally displaced persons (IDPs) in cash-for-work activities supporting agricultural production and resilience in host communities, while strengthening the capacities of 40 farmers’ cooperatives and 60 MoA staff members.
+The emergency agriculture intervention will combine cash assistance, vouchers and agricultural inputs tailored to the needs of crop producers and livestock keepers, helping vulnerable households maintain or restore productive activities, protect their livelihoods and improve food security. Particular attention will be given to women, female-headed households and other vulnerable groups disproportionately affected by the crisis.
+The programme will also strengthen the operational capacities of the Lebanese Ministry of Agriculture to support emergency response efforts, beneficiary targeting, information management and service delivery in conflict-affected areas. This component builds on the recently signed Memorandum of Understanding on cooperation in the agricultural sector between Italy and Lebanon, which provides a framework for enhanced collaboration between the two countries in support of agricultural development, food security and institutional capacity-building.
+H.E. Fabrizio Marcelli, Ambassador of Italy to Lebanon, stated:
+"Italy remains firmly committed to supporting Lebanon and its people at a time of significant humanitarian and economic challenges. By supporting FAO’s intervention, we aim to help vulnerable rural communities preserve their livelihoods, sustain agricultural production and strengthen food security in areas most affected by the conflict. This contribution also complements the growing cooperation between Italy and Lebanon in the agricultural sector, as reflected in the Memorandum of Understanding recently concluded between our two countries."
+Ms Liana De Rosa, Director of AICS Beirut, stated:
+“The Italian Cooperation responded swiftly to the escalation of hostilities by approving this emergency initiative to provide direct, tangible support to rural communities in the most affected areas. The initiative aims to ensure food security while safeguarding and restoring the disrupted livelihoods of farmers and IDPs.”
+"Every season lost puts livelihoods at risk. With the generous support of Italy, this project will provide farmers, women, men and youth, with the critical inputs and services they need to continue producing food to overcome the challenges they face, from quality seeds and fertilizers to livestock feed and vaccines and harvesting services. By promoting equitable access to resources and livelihood opportunities, we contribute to rural women and youth economic empowerment, support their families, and contribute to the recovery and resilience of their communities.” said Nora Ourabah Haddad, FAO Representative in Lebanon.
+H.E. Dr. Nizar Hani, Minister of Agriculture of Lebanon, stated:
+“The Ministry of Agriculture highly appreciates the generous contribution of The Government of Italy, through the Ministry of Foreign Affairs and International Cooperation, which once again demonstrates Italy’s steadfast commitment to supporting Lebanon and its rural communities during this critical period.
+The program, ‘Emergency and Livelihood Support in the Agrifood Sector to Conflict-Affected Areas in Lebanon,’ goes beyond emergency assistance. It represents a strategic investment in restoring agricultural production, protecting rural livelihoods and strengthening the resilience of Lebanon’s agrifood systems in the areas most affected by the conflict, particularly in southern Lebanon.
+This initiative also translates into concrete action the Memorandum of Understanding on agricultural cooperation signed between Lebanon and Italy by the Minister of Agriculture of Lebanon and his Italian counterpart, reaffirming the shared commitment of both countries to support agricultural recovery, strengthen food security and build resilient rural communities.
+By supporting vulnerable farmers, internally displaced persons, cooperatives and the Ministry’s operational capacities, the program will contribute directly to food security, economic recovery and social stability. It further reflects the strength of the strategic partnership between Lebanon, Italy and FAO and our common vision for a more resilient, inclusive and sustainable agricultural sector for the future.”
+The project reflects the continued partnership between the Government of Italy, the Ministry of Agriculture and FAO to support vulnerable rural populations and strengthen Lebanon’s agrifood systems.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:09.822798+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>International Day of Cooperatives: FAO Highlights the Role of Cooperatives in Strengthening Rural Communities in Lebanon</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/international-day-of-cooperatives--fao-highlights-the-role-of-cooperatives-in-strengthening-rural-communities-in-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>International Day of Cooperatives: FAO Highlights the Role of Cooperatives in Strengthening Rural Communities in Lebanon
+Across Lebanon, cooperatives and producer organizations support farmers, fishers, women, men and youth entrepreneurs and rural communities overcome economic challenges, improve livelihoods and strengthen resilience. By working collectively, they facilitate access to markets, services and productive resources, provide a voice in decision making, while strengthening social cohesion and local development.
+Celebrated annually on the first Saturday of July, the International Day of Cooperatives will take place on 4 July 2026, globally under the theme "Cooperatives for a Peaceful World!". On this day, The Food and Agriculture Organization of the United Nations (FAO) highlights the vital role that cooperatives and producer organisations play in achieving food security, supporting rural, coastal, and fisheries-dependent communities’ livelihoods and strengthening the resilience of Lebanon’s agrifood systems.
+At a time when rural communities continue to face the combined impacts of conflict, economic instability, climate-related challenges and rising production costs, collective action enables small-scale producers to reduce risks, improve productivity and seize new economic opportunities that would often fall beyond the reach of individuals acting alone.
+"Cooperatives are powerful organizations that offer practical solutions built on solidarity, trust and shared responsibility," said Nora Ourabah Haddad, FAO Representative in Lebanon. "When farmers, fishers and economic actors work together, they are better equipped to manage risks, realize economies of scale, increase their bargaining power, access markets and invest in their future. FAO's support goes beyond training and equipment. It is about building strong and sustainable rural institutions that continue delivering services to their members, creating opportunities and strengthening local economies for years to come."
+A flagship example of FAO’s commitment to cooperative development is its partnership with the Ministry of Agriculture and the General Directorate of Cooperatives, supported by the Government of Canada. Between 2019 and 2024, the programme strengthened more than 250 women-led groups across the country. A total of 265 groups received technical and business development training, while 143 groups were equipped with productive assets that enabled them to expand collective food processing activities, improve product quality and generate income.
+The programme also strengthened the institutional capacities of the General Directorate of Cooperatives, enhancing its ability to support, monitor and coordinate cooperative development nationwide.
+With funds from the government of Canada, FAO supported the General Directorate of Cooperatives by strengthening its Management Information System, which hosts sex-disaggregated data from cooperatives for improved analysis, management and coordination.
+“In a world often divided, cooperatives remind us that true strength lies not in competition but in joining efforts. Through solidarity, trust and cooperative values we build a better world” said Gloria Abouzeid, Director-General of Cooperatives at the Ministry of Agriculture.
+Building on these achievements and on the impact of the achieved results of the Canada-funded project, FAO continues to promote farmers’ collective action across Lebanon’s agrifood systems. FAO is advancing an integrated and programmatic approach to collective action to drive inclusive and sustainable agrifood systems transformation in Lebanon. This approach is structured around three core pillars: strengthening institutions and dialogue platforms; promoting climate-smart agriculture; and enhancing governance, management, and rural finance capacities. By embedding collective action across its programme portfolio, FAO Lebanon strengthens alignment between policy support and field-level interventions, enabling scalable and lasting impact.
+In addition, through cooperatives, producer organisations and other community-based organisations, FAO contributes to empowering rural communities to strengthen governance, increase women's and youth participation, enhance access to services and markets, and build resilience to climate-related and economic shocks.
+In the water sector, funded by the Swiss Government, FAO supports Water User Associations to improve the equitable and sustainable management of scarce water resources. In fisheries, funded by Norway, FAO works with fisheries cooperatives to strengthen governance, business management and service delivery, contributing to more sustainable livelihoods for coastal communities. Similar approaches are being expanded through livestock programmes, where producer organizations help small-scale producers improve productivity, meet quality standards and better access markets, under projects funded by the World Bank and the European Union.
+Strong and inclusive cooperatives are essential partners in building resilient, sustainable and competitive agrifood systems. By fostering democratic participation, strengthening local economies and creating opportunities for rural women and men alike, they contribute not only to food security and economic development, but also to building peace and cohesion within rural communities.
+On this International Day of Cooperatives, FAO reaffirms its commitment to working alongside the Ministry of Agriculture, the General Directorate of Cooperatives and development partners to strengthen collective action as a driver of food security, rural prosperity, sustainable development and resilient agrifood systems across Lebanon.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:16.108220+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, the EU, FAO and WFP Drive Coordinated Action to Support Food Security and Rural Livelihoods in Lebanon</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/ministry-of-agriculture--the-eu--fao-and-wfp-drive-coordinated-action-to-support-food-security-and-rural-livelihoods-in-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, the EU, FAO and WFP Drive Coordinated Action to Support Food Security and Rural Livelihoods in Lebanon
+©FAO/Elite Sfeir
+The Ministry of Agriculture, in collaboration with the European Union (EU), the Food and Agriculture Organization of the United Nations (FAO), the World Food Programme (WFP) is advancing a joint EU-funded initiative aimed at enhancing food security farmers across Lebanon by supporting Lebanon’s agriculture.
+As part of these efforts, the Lebanese Minister of Agriculture convened a high-level meeting with FAO Representative in Lebanon, Nora Ourabah Haddad, WFP Representative and Country Director, Allison Oman Lawi and Cyril Dewaleyne, Deputy Head of Cooperation at the EU Delegation to Lebanon, alongside technical teams from the Ministry, FAO, WFP and the EU.
+The meeting provided strategic guidance and endorsed key decisions and implementation modalities in light of the current context in Lebanon, ensuring the continued effective rollout of the project “Contributing to Food Security for Refugees and Host Communities Living in Lebanon.”
+Funded by the European Union, the project focuses on strengthening the productive capacity of farmers through cash-based support, technical training and rehabilitation of agricultural assets. It supports land rehabilitation through grants, development of irrigation infrastructure such as hill lakes and irrigation schemes, and improved access to water resources, while also reinforcing institutional capacities related to agricultural inputs and production systems.
+This initiative highlights the central role of the Ministry of Agriculture in leading national agricultural policies and strengthening administrative and technical systems. It also reinforces Lebanon’s commitment to supporting its agricultural sector as a key pillar for economic development and resilience.
+Minister of Agriculture, Dr. Nizar Hani said: “Strengthening food security in Lebanon is no longer merely an option; it has become a national and strategic priority directly linked to the resilience of rural communities and to the country’s economic and social stability. In this context, the advanced partnership between the Ministry of Agriculture, the European Union, the Food and Agriculture Organization of the United Nations (FAO), and the World Food Programme (WFP) represents an effective model of coordinated development action that supports people, land, and sustainable production simultaneously.”
+He added: “We firmly believe that investing in agriculture is an investment in stability, food sovereignty, and sustainable development. Accordingly, we are working to strengthen farmers’ capacities, improve agricultural infrastructure, and enhance the management of natural resources in order to ensure the continuity of production and increase the Lebanese agricultural sector’s ability to withstand ongoing challenges and crises. The expansion of the agricultural registry, alongside the provision of technical training, financial assistance, and rehabilitation support to thousands of farmers, constitutes a fundamental step toward building a more equitable, efficient, and resilient agricultural sector. Through these initiatives, we aim to establish a sustainable development model that places Lebanese farmers at the center of economic recovery and long-term rural revitalization.”
+Minister Hani also stressed the importance of developing more focused and specialized media coverage on agricultural and rural development issues, emphasizing the essential role of the media in highlighting the importance of the agricultural sector, raising awareness about existing challenges and opportunities, and strengthening both public and international support for farmers and national food security.
+From her side, FAO Representative in Lebanon, Nora Ourabah Haddad said:
+“FAO remains committed to supporting Lebanon in strengthening resilient agrifood systems. Through this project, we are supporting farmers with cash assistance, technical training, and rehabilitation of agricultural assets, while advancing irrigation infrastructure and improving water management. These efforts are essential to restoring productive capacities, supporting rural livelihoods, and ensuring sustainable food production in the current context.”
+“After years of overlapping crises, farmers and rural families across Lebanon are facing increasing pressure on their livelihoods and food security. "By combining cash assistance with technical support and investments in agricultural infrastructure, we are enabling families not only to meet their immediate needs, but also to restore their livelihoods and build a more food-secure future. "Our continued partnership with the Ministry of Agriculture, FAO, and the European Union is essential to ensuring that no one is left behind during these challenging times,” said Anne Valand, WFP Lebanon Deputy Country Director.
+Cyril Dewaleyne, Deputy Head of Cooperation at the EU Delegation to Lebanon said: “The EU and the international community remain committed in supporting Lebanon through these difficult times. At the EU Delegation to Lebanon, we continue to work hard in supporting Lebanese farmers and institutions. The continued progress under this EUR 15 million project - fully funded by the EU - is a proof of that.” He added: The agricultural sector is one of the many hearts of this country; it has significant cultural value, it allows farmers to put food on their tables and on the tables of others, while contributing to livelihoods, the creation of communities and economic development.”
+As of April 2026, over 80 000 farmers have been registered in the Farmers Registry under the project, marking an important step toward expanding support to agricultural communities across the country. Nearly 2 000 farmers have already received cash assistance to sustain their livelihoods, while close to 2 000 farmers and agricultural workers have benefited from technical training. In parallel, key infrastructure interventions have been identified, including hill lakes and irrigation schemes, and more than 1 800 farmers have been shortlisted for field damage assessments to determine eligibility for rehabilitation support through grants.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:22.300442+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LEBANON: NEW IPC ANALYSIS SHOWS CONFLICT ESCALATION PUSHING NEARLY A QUARTER OF POPULATION INTO ACUTE FOOD INSECURITY</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/lebanon--new-ipc-analysis-shows-conflict-escalation-pushing-nearly-a-quarter-of-population-into-acute-food-insecurity/en</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LEBANON: NEW IPC ANALYSIS SHOWS CONFLICT ESCALATION PUSHING NEARLY A QUARTER OF POPULATION INTO ACUTE FOOD INSECURITY
+UN agencies and Government warn acute food insecurity is likely to deepen without sustained and timely humanitarian and livelihood support
+A sharp escalation in violence has reversed recent food security gains in Lebanon and pushed the country back into crisis. This is according to the latest Integrated Food Security Phase Classification (IPC) projected analysis released by the Ministry of Agriculture, in collaboration with the Food and Agriculture Organization of the United Nations (FAO) and the World Food Programme (WFP).
+The analysis reveals that 1.24 million people – nearly one in four of the population analysed – are expected to face food insecurity levels classified as Crisis (IPC Phase 3) or worse, between April and August 2026. This marks a significant deterioration from the period of November 2025 through March 2026, when an estimated 874,000 people, roughly 17 percent of the population, were experiencing acute food insecurity. The deterioration is due to conflict, displacement and economic pressures.
+“The fragility we warned about in the previous IPC analysis has unfortunately proven to be true,” said Allison Oman Lawi, WFP Representative and Country Director in Lebanon. “Hard won gains have been swiftly reversed. Families who were just managing to cope are now being pushed back into crisis as conflict, displacement and rising costs collide, making food increasingly unaffordable.”
+‘This confirms continued and deepening fragility in rural and agrifood systems. Compounded shocks are undermining agricultural livelihoods and impacting food security, highlighting the urgent need for emergency agricultural assistance to support farmers and prevent further deterioration, said Nora Ourabah Haddad, FAO Representative in Lebanon.
+“These results underscore the severity of the current situation in Lebanon, where conflict intersects with economic pressures putting national food security under critical risk and juncture. We reaffirm our commitment to adopting a sustainable, science-based approach that goes beyond merely monitoring crises, by responding to them through continuous policies and programmes that strengthen the resilience of the agricultural sector and protect farmers’ livelihoods.
+“We also stress the need to move beyond passive neutrality in addressing these crises to a responsible neutrality toward a more proactive and strategic approach. In this context, we consider the media, alongside international partners, as a key pillar in conveying the truth and raising awareness, to support response efforts and promote sustainable recovery.
+“Safeguarding food security in Lebanon is a shared national and international responsibility, and investment in agriculture remains essential to ensuring stability and strengthening communities’ resilience to recurring crises” said Lebanese Minister of Agriculture, Dr. Nizar Hani.
+The findings confirm that Lebanon’s food security situation remains highly sensitive to shocks. Without predictable humanitarian assistance, improved access, and stabilisation of the security and economic environment, food insecurity is likely to deepen further in the months ahead.
+The deterioration is being driven by a convergence of shocks linked to the ongoing escalation. Insecurity and displacement are disrupting livelihoods and income opportunities, while market access remains uneven in conflict affected areas as supply chains come under strain. At the same time, rising inflation and food prices continue to erode purchasing power, while reduced humanitarian assistance and funding shortfalls are limiting families’ ability to cope.
+Agriculture — a critical source of food and income — has been significantly affected and has yet to recover from the 2024 conflict. Damage to farmland, widespread displacement of farming households, restricted access to agricultural areas, rising input costs, and persistent insecurity are constraining production, while localized market disruptions are further limiting farmers’ ability to operate. Risks are intensifying as the spring planting window closes. Without urgent support, missed planting seasons will lead to production losses, deepening food insecurity and increasing humanitarian needs in the months ahead. Livestock and poultry systems are also under strain due to restricted access and disrupted services.
+Geographically, the sharpest deterioration is observed in conflict affected areas particularly in Bent Jbeil, Marjeyoun, Sour and Nabatiyeh districts, , where displacement and market disruptions are most pronounced, followed by Baalbeck El Hermel.
+Furthermore, regional dynamics are compounding the crisis. Disruptions to trade routes, rising fuel and transport costs, and increasing food prices linked to the regional conflict are further squeezing markets and household budgets.
+The crisis is affecting all population groups. Among Lebanese households, 725,000 people (19 percent) are projected to face Crisis (IPC Phase 3) or worse levels of acute food insecurity. The situation remains particularly severe among displaced and vulnerable populations, with 362,000 Syrian refugees (36 percent) and 104,000 Palestinian refugees (45 percent) classified in Crisis or worse. Newly arrived populations from Syria since 2024 are among the most affected, with around 50,000 people (52 percent) projected to face acute food insecurity.
+At these levels, households are no longer able to consistently meet their basic food needs and are increasingly forced to reduce the quantity and quality of food consumed, skip meals, or resort to harmful coping strategies such as taking on debt or selling essential assets to survive.
+As the analysis reflects conditions in the immediate aftermath of the current escalation, the full effects of the conflict escalation and wider regional war may not yet be fully reflected in currently available evidence, as such actual outcomes could deteriorate further should these pressures intensify or persist for longer than currently assumed.
+Sustained and timely humanitarian and livelihoods assistance is critical to protect the most vulnerable, safeguard livelihoods and prevent a deeper food security crisis.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:29.414790+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Empowering Women in Crisis: FAO Keeps Lebanon’s Farmers Connected</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/empowering-women-in-crisis--fao-keeps-lebanon-s-farmers-connected/en</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Empowering Women in Crisis: FAO Keeps Lebanon’s Farmers Connected
+©FAO/ Ralph Azar
+As the crisis in Lebanon continues to restrict movement and access to several rural areas, FAO Lebanon rapidly adapted its support to farmers by shifting its outreach modality from field-based assistance to using remote communication tools since early March.
+This ensured continuity of support to vulnerable farming communities at a critical moment. By leveraging existing communication groups already trusted by farmers, FAO maintained a steady flow of information and engagement despite access constraints. Regular messages and check-in calls created a reliable support system, helping farmers stay informed, connected and supported throughout the crisis.
+To maximize reach and inclusivity, FAO’s Gender and Inclusion Team developed simple visual materials and voice messages. These tools were designed to overcome literacy barriers and ensure accessibility for all farmers, particularly women and vulnerable groups.
+The content was continuously adapted to reflect evolving needs on the ground, addressing not only agricultural concerns but also critical social issues such as stress, displacement, shared decision-making, gender-based violence and safety.
+Five easy-to-understand infographics and a series of voice messages were disseminated, enabling farmers to access practical information in formats suited to their circumstances. It proved particularly effective in reaching women with limited access to formal extension services.
+The intervention reached 1 193 farmers, of whom 44 percent were women, with women’s participation exceeding that of men in key agricultural regions including the Bekaa, Nabatieh, and the South. Beyond information sharing, the approach facilitated increased engagement of women in group discussions and decision-making processes.
+Evidence of impact is reflected in strong community uptake and peer-to-peer dissemination. Farmers actively shared materials within their networks, including among displaced populations. A farmer from Tripoli described the materials as “very important during these times.” Beneficiaries highlighted the value of the initiative, with one farmer noting, “We wait for your messages,” underscoring the role of FAO’s communication in providing both information and reassurance during uncertain times.
+FAO complemented awareness-raising with direct support mechanisms. Regular group calls integrated gender-sensitive facilitation alongside technical agricultural guidance, while trained staff were equipped to respond to sensitive cases and refer individuals to appropriate services. A streamlined referral pathway was established to connect farmers, including women and persons with disabilities, to additional services when needed.
+“Even from a distance, we are committed to standing by farmers in times of crisis,” said Nora Ourabah Haddad, FAO Representative in Lebanon. “Simple, inclusive communication tools such as voice messages and visual materials are proving essential for farmers to stay informed, connected, and resilient during challenging times, and therefore ensuring that no one is left behind.”
+Building on these results, FAO Lebanon will maintain this inclusive, low-cost, and adaptable communication model to sustain support to farming communities and highlight the important role women play in agriculture, food security, and family resilience during times of crisis.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:35.692640+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, FAO and Government of Canada Launch Online Training to Support Farmers Across Lebanon</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/ministry-of-agriculture--fao-and-government-of-canada-launch-online-training-to-support-farmers-across-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, FAO and Government of Canada Launch Online Training to Support Farmers Across Lebanon
+Farmer taking part in the comprehensive virtual training programme
+©FAO/ Ralph Azar
+In a step aimed at supporting the resilience of the agricultural sector amid current challenges, the Lebanese Ministry of Agriculture, in collaboration with the Food and Agriculture Organization of the United Nations, funded by the Government of Canada, has launched a comprehensive virtual training programme targeting farmers across various regions of Lebanon.
+The program aims to help farmers strengthen apple and vegetable value chains while preparing for the upcoming agricultural season. It also includes gender and protection.
+Originally planned as in-person sessions, the training has been adapted to a fully online format using WhatsApp technical messages and interactive Q&amp;A sessions to ensure continuity, safety, and broad reach across Lebanon.
+Over 2200 farmers including 883 women and 1323 men will participate in the program, gaining knowledge on good agricultural practices, crop management, and season planning. The initiative also integrates gender-sensitive approaches and inclusion guidance.
+His Excellency the Minister of Agriculture, Dr. Nizar Hani affirmed that the Ministry has developed a comprehensive response plan to keep pace with the critical phase Lebanon is going through. The plan aims to strengthen farmers’ resilience, maintain the continuity of agricultural activities as much as possible, support national food security, and reduce potential losses to the sector.
+Dr. Nizar Hani highlighted the importance of strategic partnerships that bring together the Ministry of Agriculture with donor countries, international organizations, and local entities through the Agriculture Partners Network in Lebanon, commending the efforts made to achieve sustainable agricultural and food development. He also underscored the vital role played by the Food and Agriculture Organization of the United Nations in supporting Lebanon, whether through the implementation of emergency projects or by coordinating efforts with donors.
+He expressed the Ministry’s aspiration to further strengthen this cooperation to secure additional resources and expand the scope of agricultural interventions, ensuring that support reaches the most affected farmers—both women and men—across all regions of Lebanon. He also stressed the ongoing work to develop scientific and transparent tools that help guide interventions and enhance the effectiveness of the response.
+He added: “This programme is considered an innovative model for adapting to crises and reflects the commitment of the concerned stakeholders to support farmers and strengthen the sustainability of the agricultural sector in Lebanon.”
+FAO Representative in Lebanon, Nora Ourabah Haddad, stated: "By leveraging digital tools like WhatsApp and interactive Q&amp;A sessions, we are ensuring farmers across Lebanon can continue learning, applying good agricultural practices, and making informed decisions for their crops. This approach is a model for resilience in times of crisis."
+From his side, Ambassador of Canada to Lebanon and Syria, Gregory Galligan, said:"Lebanon’s agricultural sector has been severely affected by the conflict. Through our partnership with the Ministry of Agriculture and FAO, Canada is proud to continue supporting farmers during this challenging time, with flexible learning approaches that contribute to build resilience, sustain production, and enhance food security."
+This initiative demonstrates the power of collaboration between FAO, the Lebanese Ministry of Agriculture, and international partners to support farmers, enhance resilience, and ensure agriculture continues to thrive despite challenging circumstances.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:42.603334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture and FAO launch Japan-funded project to Enhance Recovery and Resilience of Agrifood Systems and Rural Livelihoods in Conflict-Affected Areas of South Lebanon</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/ministry-of-agriculture-and-fao-launch-japan-funded-project-to-enhance-recovery-and-resilience-of-agrifood-systems-and-rural-livelihoods-in-conflict-affected-areas-of-south-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture and FAO launch Japan-funded project to Enhance Recovery and Resilience of Agrifood Systems and Rural Livelihoods in Conflict-Affected Areas of South Lebanon
+©FAO/ Ralph Azar
+The Ministry of Agriculture and the Food and Agriculture Organization of the United Nations (FAO) in Lebanon, has launched a new project “Enhancing Recovery and Resilience of Agrifood Systems and Rural Livelihoods in Conflict-Affected Areas of South Lebanon” funded by the Government of Japan.
+The initiative will support agriculture-based livelihoods for approximately 230 vulnerable farming households, representing 1 150 individuals, engaged in crop and livestock production across the South and Nabatiyeh governorates. The project will help families maintain food production and income generation while strengthening local agrifood systems. At least 30 percent of beneficiaries will be women, including female-headed households.
+Designed to respond to the urgent needs of rural communities affected by the ongoing conflict, the project will safeguard livelihoods, restore agricultural production, and strengthen resilience to future shocks. Through tailored support packages, smallholder farmers will receive targeted assistance to safeguard production and animal assets.
+Lebanese Minister of Agriculture, Dr. Nizar Hani said: “This project comes at a pivotal moment for the agricultural sector in South Lebanon, where the challenges of conflict intersect with mounting climate and economic pressures. This reality calls for a comprehensive, science-based approach to rebuilding agricultural and food systems on more resilient and sustainable foundations.” He added: “In partnership with the Food and Agriculture Organization (FAO) and the Government of Japan, we are working to shift from emergency response to sustainable recovery by supporting smallholder farmers and strengthening their capacity to safeguard their productive assets—particularly livestock, which remains a cornerstone of rural food security.”
+“This initiative goes beyond immediate assistance. It is embedded within a broader national vision aimed at revitalizing agricultural value chains, improving natural resource management, and fostering agricultural innovation to ensure continuity of production and enhanced livelihoods. We also place special emphasis on empowering rural women, recognizing their central role in food systems and their contribution to advancing social equity and balanced development. Today, the resilience of the agricultural sector is fundamental to Lebanon’s overall resilience. Investing in agriculture is an investment in stability, food sovereignty, and the future of coming generations” he concluded.
+“The intervention responds to the most immediate and critical needs identified by the Ministry of Agriculture, particularly emergency fodder support for small-scale livestock keepers,” said FAO Representative in Lebanon a.i, Etienne Careme. “Animals cannot wait for access to be restored. Without immediate support, herds risk being lost, along with the primary livelihood asset of the most vulnerable households in the project’s target areas.”
+Ambassador of Japan to Lebanon, Yokota Kenji said: “Through this partnership with the Food and Agriculture Organization, and in close collaboration with the Ministry of Agriculture, Japan aims to support the recovery of Lebanon’s agrifood sector, strengthen food security, and enhance the resilience and livelihoods of small-scale farmers affected by the recent conflict. Japan remains firmly committed to standing alongside Lebanon and its people during these challenging times.”
+This initiative reflects the strong strategic partnership between Lebanon, FAO, and the Government of Japan in supporting rural communities, protecting agricultural livelihoods, and promoting sustainable recovery in conflict-affected areas.
+Through timely and coordinated assistance, farmers can continue producing food, sustaining their households, and contributing to local economies.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:49.059293+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FAO Lebanon scales up emergency support to protect agriculture and food security in Lebanon</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/fao-lebanon-scales-up-emergency-support-to-protect-agriculture-and-food-security-in-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>FAO Lebanon scales up emergency support to protect agriculture and food security in Lebanon
+©FAO Lebanon/ Ralph Azar
+According to a Summary of Agricultural Damage Assessment published by the Ministry of Agriculture, 1 987 farmers remain in affected areas, while 2,503 farmers have expressed their need for financial support due to displacement and damage to agricultural production. The poultry production sector has also experienced a 27 percent increase in damage over the past week.
+The Food and Agriculture Organization of the United Nations is strengthening its support to Lebanon’s agriculture sector to help safeguard food and nutrition security amid the escalating conflict. Rural communities, already disproportionately affected by poverty and food insecurity, are facing damaged farmlands, shortages of agricultural inputs and livestock feed, and disrupted agrifood markets.
+As livelihoods come under increasing pressure, many households are being pushed toward negative coping mechanisms. In response, FAO is scaling up emergency and resilience assistance across the country to help farmers sustain production and protect their sources of income.
+“Protecting agriculture is essential to ensuring food security and sustaining rural livelihoods during this critical time,” said Nora Ourabah Haddad, FAO Representative in Lebanon. “By providing timely support to farmers and livestock producers, we aim to help communities maintain production, preserve incomes and strengthen their resilience in the face of ongoing challenges.”
+In support of national efforts, FAO Lebanon is prioritizing assistance to the most vulnerable crop and livestock producers by providing critical inputs and targeted support to sustain production and livelihoods. FAO will also continue to deliver evidence-based analyses to inform the humanitarian response to the crisis and its impact on food security and agriculture, while promoting self-reliance and reducing aid dependency.
+FAO is continuing to expand its support in coordination with partners to address the evolving needs of Lebanon’s agriculture sector. The organization is currently delivering across a portfolio of 17 projects and around 200 activities nationwide aimed at maintaining agricultural production, protecting rural livelihoods and informing targeted response efforts.
+Despite access constraints, 91 percent of activities remain ongoing, adapted or accelerated through flexible implementation modalities, while only 9 percent are temporarily paused due to security conditions. FAO is also sustaining support to farmers and core programmes through remote management and close coordination with the Ministry of Agriculture (MoA).</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:41:55.600688+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture and FAO Hold Phytosanitary Capacity Evaluation Workshop to Strengthen Lebanon’s Plant Health System</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/ministry-of-agriculture-and-fao-hold-phytosanitary-capacity-evaluation-workshop-to-strengthen-lebanon-s-plant-health-system/en</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture and FAO Hold Phytosanitary Capacity Evaluation Workshop to Strengthen Lebanon’s Plant Health System
+Phytosanitary Capacity Evaluation Workshop
+©FAO Lebanon/Elite Sfeir
+The Ministry of Agriculture, in collaboration with the Food and Agriculture Organization of the United Nations (FAO) in Lebanon, successfully conducted the first Phytosanitary Capacity Evaluation (PCE) workshop, focusing on the “Situation Analysis” phase. The workshop brought together national stakeholders and technical experts to assess and strengthen Lebanon’s phytosanitary system.
+The event was organized under the project “Supporting national capacities to conduct a Phytosanitary Capacity Evaluation (PCE) enhancing Lebanon’s compliance with international phytosanitary standards.” It marked an important step toward identifying gaps and defining priority actions to improve plant health governance and compliance with international standards.
+During the workshop, participants increased their knowledge about the International Plant Protection Convention (IPPC), Sanitary and Phytosanitary (SPS) measures, the different steps of the Phytosanitary Capacity Evaluation (PCE), and the role of the National Plant Protection Organization (NPPO) in supporting agricultural production and trade.
+Representatives from the Ministry of Agriculture, FAO, and relevant national institutions engaged in a roundtable discussion to assess the current status of Lebanon’s phytosanitary system. Discussions focused on key PCE modules related to export certification, import regulations, NPPO structures and processes, and pest free areas, aiming to identify challenges affecting the system’s effectiveness.
+Participants highlighted the importance of strengthening phytosanitary capacities to support Lebanese agricultural exports. Currently concentrated in a limited number of markets, mainly in the Gulf region, exports face increasing international sanitary and phytosanitary requirements. Enhancing national compliance systems is essential to facilitate access to diverse markets and expand trade opportunities for Lebanese agricultural products.
+“The Ministry of Agriculture places plant health at the top of its priorities, given its direct impact on agricultural production, quality standards, and Lebanon’s competitiveness in international markets. We are fully committed to the Phytosanitary Capacity Evaluation process and consider it a strategic step toward strengthening our national system. The Ministry will provide full support to enhance the capacities of the National Plant Protection Organization, improve compliance mechanisms, and ensure the protection of our agricultural production while expanding export opportunities for Lebanese farmers” stated Dr. Nizar Hani, Minister of Agriculture.
+“Through this initiative, FAO continues to support the Ministry of Agriculture in reinforcing plant health systems, protecting agricultural production, safeguarding farmers’ livelihoods, and contributing to more resilient and sustainable agri-food systems in Lebanon” noted Etienne Careme, FAO Lebanon Resilience and Liaison Officer.
+The outcomes of the workshop will inform the next phases of the PCE process, guiding future actions and investments aimed at strengthening Lebanon’s compliance with international phytosanitary standards and enhancing the country’s agricultural competitiveness</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:42:02.362248+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Supporting Fodder Production to Strengthen Livestock and Food Security in Lebanon</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/supporting-fodder-production-to-strengthen-livestock-and-food-security-in-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Supporting Fodder Production to Strengthen Livestock and Food Security in Lebanon
+Distribution of fodder seeds across Lebanon
+©FAOLebanon
+Across Lebanon, 657 farmers (26 percent are female farmers) have benefited from the distribution of fodder seeds under a joint project implemented by the Ministry of Agriculture in collaboration with the Food and Agriculture Organization of the United Nations (FAO). A total of 86 tonnes of wheat seeds, 15 tonnes of vetch, 12 tonnes of oat, and 18 tonnes of triticale were distributed to farmers, with quantities allocated based on the size of the area each farmer could cultivate under the project. The total area to be cultivated is 775 Ha.
+This support is part of a wider programme that aims to strengthen rural development and improve food security across Lebanon. This 4,500,000 US$ initiative is financed through the PROSPECTS program, the Global Partnership for Improving Prospects for Forcibly Displaced Persons and Host Communities, administered by the World Bank, and focuses on supporting investments in the milk and dairy sector.
+For many farmers, this assistance is not only about seeds but also about survival and sustaining livelihoods. In Akkar, woman farmer Noha Al Shaykh describes how the production of local fodder is already alleviating her situation. “Producing fodder locally has greatly helped me reduce the cost of purchasing ready-made feed, especially given the continuous rise in prices” she says. She also describes how her access to fodder has a direct effect on the health of her animals, resulting in better nutrition and overall stability. “This step is very important to me, as it has allowed me to continue raising livestock despite the increasing costs. I plan to continue growing fodder because it has become a necessity rather than just an experiment.”
+In South Lebanon, farmer Fady Shebli considers the project a base for growth. “This project is a step in the right direction,” he says. “I got 85 kilograms of seeds, which helped me lay a foundation for the future so that I can develop my project.” For Fady, the more fodder he produces, the more he can develop his livelihood. “The more fodder I have, the more animals I'm able to raise." he adds.
+Fodder production is a cornerstone of Lebanon’s agricultural sector. It directly supports livestock systems that provide essential food products such as milk, meat, and dairy, while helping farmers sustain their livelihoods.
+The intervention combines cash assistance with practical support. Farmers receive quality fodder seeds, fodder hand harvesters, and technical training covering both planting and harvesting.
+By improving access to inputs and know-how, the initiative will help farmers reducing feeding costs, lower overall production expenses, and improve animal performance with expected productivity gains of 10–20 percent and improved profitability and sustainability of livestock enterprises. This is particularly significant in Lebanon, where feed accounts for around 70 percent of livestock production costs.
+The project enhances livestock productivity by supporting participating farmers with drought-resistant and climate-resilient fodder varieties that offer higher yields, improved digestibility, and superior nutritional value. These interventions are supported through the establishment of demonstration fodder plots and comprehensive technical guidance and training delivered by the Lebanese Agricultural Research Institute (LARI). The capacity building activities promote improved fodder management practices, aiming to optimize input use, strengthen climate resilience, and increase overall production potential
+As fodder production faces increasing pressure from limited arable land, water scarcity, economic instability, and climate change, the project is helping reduce farmers’ reliance on imported feed, strengthen the resilience of the livestock sector, and protect the livelihoods of farming households, especially those headed by women across Lebanon.
+Background on the project
+The project will support approximately 3,175 farms engaged in the dairy sub-sector and feed production across Lebanon. It will benefit vulnerable small scale Lebanese farmers and displaced populations, offering matching grants and technical support to enhance productivity, increase yields, and improve working conditions on farms.
+The project will also contribute to structuring and developing the dairy value chain through a demand-driven approach and transformative partnerships between Lebanese farmers and off-takers. The investments would mainly consist of energy-efficient infrastructure and equipment in the dairy sector.
+In parallel, the initiative will strengthen the Ministry of Agriculture’s service delivery through innovative digital tools. It will also finance mobile veterinary clinics and laboratories to reinforce MoA’s veterinary and livestock support services.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:42:08.750287+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FAO Provides Emergency Support to the Ministry of Agriculture to Control Foot and Mouth Disease Outbreak in Lebanon</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/fao-provides-emergency-support-to-the-ministry-of-agriculture-to-control-foot-and-mouth-disease-outbreak-in-lebanon/en</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>FAO Provides Emergency Support to the Ministry of Agriculture to Control Foot and Mouth Disease Outbreak in Lebanon
+©FAO Lebanon/Ralph Azar
+The Food and Agriculture Organization of the United Nations (FAO) in Lebanon announced today the provision of emergency support to the Ministry of Agriculture (MoA) to support its efforts in controlling the Foot and Mouth Disease (FMD) outbreak affecting the country’s livestock sector.
+The project was officially signed today by the Minister of Agriculture, H.E. Dr. Nizar Hani, and the FAO Representative in Lebanon, Nora Ourabah Haddad, marking a significant step in strengthening the national response to the outbreak.
+Through this initiative, FAO will directly support the Government of Lebanon by prioritizing the implementation of the second phase of the emergency vaccination campaign of the cattle and small ruminants, strengthening the capacity development of breeders through awareness raising and targeted technical support, developing standard operating procedures for disease surveillance and response, and establishing a recurring situation report to closely monitor the outbreak and inform timely decision-making..
+Minister of Agriculture Dr. Nizar Hani stated: “I extend my deepest appreciation and gratitude to the team of the Directorate of Animal Resources at the Ministry of Agriculture for their professionalism and tireless efforts in safeguarding this strategic sector and strengthening its resilience in the face of ongoing challenges. I also express my sincere thanks to all partners and supporting institutions whose contributions help advance these efforts, reinforce sustainability, and promote the development of livestock production in line with the highest standards.
+My greatest tribute goes to the steadfast breeders across Lebanon, who continue to prove that they are the first line of defense in protecting the nation’s animal wealth and a fundamental pillar of national food security. Supporting and protecting them remains a firm priority, as the continuity of this sector is not merely an economic necessity, but a sovereign choice directly linked to Lebanon’s stability and its ability to secure its food supply.”
+“By strengthening veterinary services and laboratories, and by supporting livestock farmers in disease diagnosis, vaccination and biosecurity, this project will enhance the Government’s capacity to respond to current and future FMD threats thereby supporting food security in Lebanon,” said Nora Ourabah Haddad, FAO Representative in Lebanon. “This intervention will contribute to sustaining the livestock sector, protecting rural livelihoods, and increasing the sector’s overall resilience.” She added that “the proposed intervention aligns with FAO’s emergency response priorities and the Ministry of Agriculture’s national strategy, ensuring both the immediate containment of the outbreak and the long-term resilience of the livestock sector against similar shocks and threats to achieve food security.”
+Following the detection of the first suspected FMD cases in November 2025, the Ministry of Agriculture, in coordination with FAO and other partners, intensified surveillance and response measures within the resources available. Several coordination meetings were held, and a national FMD taskforce was established, with FAO actively participating and providing technical expertise.
+The national vaccination campaign against Foot and Mouth Disease has been ongoing for 46 days (since 20 December 2025). To date, approximately 44 000 heads of cattle have been vaccinated across 5 405 farms. The Ministry of Agriculture teams are currently completing the second dose for cattle, with around 25 000 heads vaccinated so far, while simultaneously starting the first dose for sheep and goats, which has reached approximately 66 000 heads of cattle to date.
+FAO’s emergency support aims to reinforce these efforts, limit the spread of the disease, and strengthen Lebanon’s preparedness and response capacity to protect animal health, achieve food security, and enhance rural livelihoods.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:42:15.839648+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Lebanon Validates Strategic Framework and SESA Scoping for the National Agriculture Strategy 2026–2035</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/lebanon-validates-strategic-framework-and-sesa-scoping-for-the-national-agriculture-strategy-2026-2035/en</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Lebanon Validates Strategic Framework and SESA Scoping for the National Agriculture Strategy 2026–2035
+Held in the presence of H.E. the Minister of Agriculture, Dr. Nizar Hani, and FAO Representative in Lebanon, Ms. Nora Ourabah Haddad, the workshop gathered representatives from the Ministry of Agriculture, line ministries and public agencies, the international community, civil society, academia and the private sector.
+©FAO Lebanon/ Elite Sfeir
+The Ministry of Agriculture (MoA), in collaboration with the Food and Agriculture Organization of the United Nations (FAO), organized a national workshop to validate the Strategic Framework of the Lebanon National Agriculture Strategy (NAS) 2026–2035 and the Strategic Environmental and Social Assessment (SESA) scoping. This marks a key milestone in defining national agricultural priorities and supporting long-term sector development.
+Held in the presence of H.E. the Minister of Agriculture, Dr. Nizar Hani, and FAO Representative in Lebanon, Ms. Nora Ourabah Haddad, the workshop gathered representatives from the Ministry of Agriculture, line ministries and public agencies, the international community, civil society, academia and the private sector.
+Participants emphasized the importance of finalizing and endorsing the NAS and SESA and ensuring adequate support for their implementation to drive the transformation and sustainable development of the sector.
+Building on lessons learned from the NAS 2020–2025, the new Strategy addresses both emergency and structural challenges facing the sector and contributes to national food security, resilience and sustainable economic growth.
+The preparation of the NAS 2026–2035 was launched in May 2025 under the leadership of the Ministry of Agriculture, with technical support from FAO. In parallel, a Strategic Environmental and Social Assessment is being conducted to ensure that environmental sustainability, social inclusion and resilience considerations are fully integrated into the Strategy.
+FAO reaffirmed its commitment to supporting the Ministry of Agriculture as a trusted technical partner, working closely with national stakeholders to enable effective implementation of the Strategy through strong coordination, partnerships and evidence-based approaches.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:42:22.363769+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Launching of the rehabilitation and waste management of El-Bared canal irrigation system project</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Launching-of-the-rehabilitation-and-waste-management-of-El-Bared-canal-irrigation-system-project/en</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Launching of the rehabilitation and waste management of El-Bared canal irrigation system project
+On Tuesday, February 25, 2020, the Food and Agriculture Organization of the United Nations in Lebanon, in collaboration with the Ministry of Water and Energy and the North Lebanon Water Establishment, launched the project “Rehabilitation and waste management of El-Bared Canal Irrigation System to reduce source-to-sea pollution and improve the livelihoods in the Akkar Region of Lebanon” funded by Norway. The project focuses on minimizing discharges of waste from El-Bared system to the Mediterranean Sea.
+The event took place in the presence of Mr. Maurice Saade, FAO Representative in Lebanon, Mr. Khaled Obeid, Director General of the North Lebanon Water Establishment (NLWE), Mrs. Manal Kortam, Senior Program Officer at the Norwegian Embassy, representatives from the Ministry of Energy and Environment, the Ministry of Agriculture, the North Lebanon Water Establishment (NLWE) and representatives from NGOs, INGOs, and UN agencies.
+The project, which ends in February 2022, aims at improving the livelihoods of the people utilizing the system through solid waste disposal, rehabilitation of irrigation canal systems, improved agricultural output and job creation.
+It will be working on rehabilitating the irrigation canal systems and installing trash removal structures through the employment of local labor, expanding and strengthening the water quality monitoring at key locations across the irrigation canal system and building the capacity of the North Lebanon Water Establishment on water quality monitoring and water pollution prevention. The project will also be raising awareness of pollution among the local community to improve the collection of solid waste around the irrigation canal systems.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:42:36.346159+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FAO shares on-going progress in water resources management with stakeholders</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/FAO-shares-on-going-progress-in-water-resources-management-with-stakeholders/en</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>FAO shares on-going progress in water resources management with stakeholders
+Within the project “Improved Water Resources Monitoring System/Integrated Water Resources Management at regional level in Lebanon” funded by the Swiss Embassy, the Food and Agriculture Organization of the United Nations (FAO), in collaboration with the Ministry of Energy and Water (MoEW) and the North Lebanon Water Establishment (NLWE) organized a platform meeting on February 25, 2020.
+The meeting aimed at presenting the ongoing outputs of the project to stakeholders in the country and at showing the on-going progress of the project and the way forward.
+It took place in the presence of Mr. Maurice Saade, FAO Representative in Lebanon, Mr. Khaled Obeid, Director General of the North Lebanon Water Establishment (NLWE) and Mr. Philipp Buetler, Head of International Cooperation at the embassy of Switzerland in Lebanon. Representatives from the Ministry of Energy and Environment, the Ministry of Agriculture, the North Lebanon Water Establishment (NLWE), the Litani River Authority, and representatives from NGOs, INGOs, and UN agencies also participated in the meeting.
+“This impressive number of participants urge us to increase our efforts in sharing our acquired knowledge through this project,” said Mr. Saade.
+For Mr. Obeid, this project is a new start and it paves the way to dealing with new projects differently.
+Mr. Buetler believed that this platform meeting aims at discovering more and new synergies and complementarities in the project.
+Funded by the Government of the Swiss Confederation, the project focuses on the monitoring of water resources to improve data availability, raising the capacity of water establishment personnel as well as farmers, and, thereby, providing the basis for informed decision-making power to be transferred to end-users to contribute to raising water productivity and improving water quality.
+FAO, in collaboration with the private sector, has established fifty monitoring locations in Mhamara, Bebnine, and Menieh in North Lebanon, in Nahr El-Bared Watershed. Thirty of these locations have been supplied with monitoring equipment that ranges from Parshall flumes, gauges and bar screens. In the other twenty locations, data loggers have been installed with their sensors to capture and record real-time water discharge.
+At the same time, the NLWE is provided with a capacity-building program on the operation and maintenance of the monitoring system along with the relevant procedures of data collection.
+In relation to water quality monitoring, laboratories in Menieh, Halba, Sir Al Dineyeh, and the Tripoli central laboratories have been supplied with the needed material and equipment for proper irrigation water quality testing.
+In parallel, FAO trained laboratory technicians on various parameters of irrigation water testing and analysis that should be regularly. A water collection protocol has also been developed and will be shared with Laboratory staff as a reference for optimal practices.
+In addition, a total of fifteen plot trials have been already selected, diagnosed and benchmarked. A set of recommended optimal agricultural practices to enhance water productivity has been established and is currently being implemented on-farm level. At this phase and with the support of MoA, agricultural practices at the farm level are being applied and knowledge has been transferred to farmers to enhance water productivity, thus increase food production and food security.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:42:42.642994+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FAO shares on-going progress in water resources management with stakeholders</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-shares-on-going-progress-in-water-resources-management-with-stakeholders/en</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>FAO shares on-going progress in water resources management with stakeholders
+Within the project “Improved Water Resources Monitoring System/Integrated Water Resources Management at regional level in Lebanon” funded by the Swiss Embassy, the Food and Agriculture Organization of the United Nations (FAO), in collaboration with the Ministry of Energy and Water (MoEW) and the North Lebanon Water Establishment (NLWE) organized a platform meeting on February 25, 2020.
+The meeting aimed at presenting the ongoing outputs of the project to stakeholders in the country and at showing the on-going progress of the project and the way forward. 
+It took place in the presence of Mr. Maurice Saade, FAO Representative in Lebanon, Mr. Khaled Obeid, Director General of the North Lebanon Water Establishment (NLWE) and Mr. Philipp Buetler, Head of International Cooperation at the embassy of Switzerland in Lebanon. Representatives from the Ministry of Energy and Environment, the Ministry of Agriculture, the North Lebanon Water Establishment (NLWE), the Litani River Authority, and representatives from NGOs, INGOs, and UN agencies also participated in the meeting. 
+“This impressive number of participants urge us to increase our efforts in sharing our acquired knowledge through this project,” said Mr. Saade. 
+For Mr. Obeid, this project is a new start and it paves the way to dealing with new projects differently. 
+Mr. Buetler believed that this platform meeting aims at discovering more and new synergies and complementarities in the project. 
+Funded by the Government of the Swiss Confederation, the project focuses on the monitoring of water resources to improve data availability, raising the capacity of water establishment personnel as well as farmers, and, thereby, providing the basis for informed decision-making power to be transferred to end-users to contribute to raising water productivity and improving water quality. 
+FAO, in collaboration with the private sector, has established fifty monitoring locations in Mhamara, Bebnine, and Menieh in North Lebanon, in Nahr El-Bared Watershed. Thirty of these locations have been supplied with monitoring equipment that ranges from Parshall flumes, gauges and bar screens. In the other twenty locations, data loggers have been installed with their sensors to capture and record real-time water discharge. 
+At the same time, the NLWE is provided with a capacity-building program on the operation and maintenance of the monitoring system along with the relevant procedures of data collection. 
+FAO, in collaboration with the National Council for Scientific Research (CNRS), has also developed a remote sensing-based water accounting tool at a regional level. This tool allows the monitoring of Land-cover/Land-use maps through remote sensing and generates information regarding soil moisture, vegetation state, leaf area index, biomass production, and evapotranspiration. 
+At a later stage, this information will feed into the SCADA system that will be installed to generate irrigation water accounting information to support decision-making and efficient water management. 
+In this context, FAO will organize capacity-building training for the NLWE staff to operate and analyze the produced maps and reports. 
+In relation to water quality monitoring, laboratories in Menieh, Halba, Sir Al Dineyeh, and the Tripoli central laboratories have been supplied with the needed material and equipment for proper irrigation water quality testing. 
+In parallel, FAO trained laboratory technicians on various parameters of irrigation water testing and analysis that should be regularly. A water collection protocol has also been developed and will be shared with Laboratory staff as a reference for optimal practices. 
+In addition, a total of fifteen plot trials have been already selected, diagnosed and benchmarked. A set of recommended optimal agricultural practices to enhance water productivity has been established and is currently being implemented on-farm level. At this phase and with the support of MoA, agricultural practices at the farm level are being applied and knowledge has been transferred to farmers to enhance water productivity, thus increase food production and food security.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:42:49.035209+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Launching of the rehabilitation and waste management of El-Bared canal irrigation system project</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/Launching-of-the-rehabilitation-and-waste-management-of-El-Bared-canal-irrigation-system-project/en</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Launching of the rehabilitation and waste management of El-Bared canal irrigation system project
+On Tuesday, February 25, 2020, the Food and Agriculture Organization of the United Nations in Lebanon, in collaboration with the Ministry of Water and Energy and the North Lebanon Water Establishment, launched the project “Rehabilitation and waste management of El-Bared Canal Irrigation System to reduce source-to-sea pollution and improve the livelihoods in the Akkar Region of Lebanon” funded by Norway. The project focuses on minimizing discharges of waste from El-Bared system to the Mediterranean Sea.
+The event took place in the presence of Mr. Maurice Saade, FAO Representative in Lebanon, Mr. Khaled Obeid, Director General of the North Lebanon Water Establishment (NLWE), Mrs. Manal Kortam, Senior Program Officer at the Norwegian Embassy, representatives from the Ministry of Energy and Environment, the Ministry of Agriculture, the North Lebanon Water Establishment (NLWE) and representatives from NGOs, INGOs, and UN agencies. 
+The project, which ends in February 2022, aims at improving the livelihoods of the people utilizing the system through solid waste disposal, rehabilitation of irrigation canal systems, improved agricultural output and job creation. 
+It will be working on rehabilitating the irrigation canal systems and installing trash removal structures through the employment of local labor, expanding and strengthening the water quality monitoring at key locations across the irrigation canal system and building the capacity of the North Lebanon Water Establishment on water quality monitoring and water pollution prevention. The project will also be raising awareness of pollution among the local community to improve the collection of solid waste around the irrigation canal systems.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:42:55.387881+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Planning forest management for future generations</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Planning-forest-management-for-future-generations/en</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Planning forest management for future generations
+“We have to prepare the forests of the future so that future generations can also benefit from them”, said Fady Asmar, FAO project manager during a recent training on forest management. The training was organized by FAO in collaboration with the Ministry of Agriculture, in the context of the FAO project “Smart Adaptation of Forest Landscapes in Mountain Areas” (SALMA).
+Sixteen engineers and forest guards, including eight women, from the department of the Rural Development and Natural Resources at the Lebanese Ministry of Agriculture, participated in the training on the third and fourth of February 2020. They were introduced to the principles and practices of sustainable forest management planning. The participants raised and discussed the issue of fire and post-fire plans management, as well as questions such as: what is the best time for pruning? When to apply tree thinning? What is the difference between selective cutting, recovery and improvement cutting? How to sustain forests by managing their production?
+The trainers answered all of these questions using practical and clear information and pictures.
+The training was an opportunity for participants to exchange expertise, share different points of view regarding forest planning and management, and build their capacities in these topics. They are expecting a field visit to apply the theories and concepts they have been trained on.
+The “Smart Adaptation of Forest Landscapes in Mountain Areas” (SALMA) is a project implemented by the Food and Agriculture Organization (FAO) in close collaboration with the Ministry of Agriculture (MoA) and funded by the Global Environmental Facility (GEF). It is the largest FAO forestry project in the Near East Region. The project aims at enhancing the resilience of vulnerable rural communities, their livelihoods in mountain areas by increasing the forest cover and implementing sustainable forest management.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:01.973822+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FAO Lebanon prepares the ground for a national fishing vessel census</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/FAO-Lebanon-prepares-the-ground-for-a-national-fishing-vessel-census/en</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>FAO Lebanon prepares the ground for a national fishing vessel census
+On a windy day in January 2020, fishermen in the Okaibeh port, in Mount Lebanon, sell their freshly caught fish, sorted according to the species. Others mend their nets in preparation for their next fishing trip.
+The Okaibeh fishermen shared stories and aspirations with fishing experts Mr. Ahmad AlMazraoui, Mr. Marouene Bdioui from FAO and Mr. Nicola Ferri from GFCM, in the context of a mission carried out from the 25th until the 31st of January 2020, with the support of the Lebanese Ministry of Agriculture.
+In addition to the Okaibeh port, FAO international and local fisheries experts and Ministry of Agriculture experts visited Jounieh, Abdeh, Saida, Sarafand, Tyr, Al Mina/Tripoli and Dora ports conducting interviews with fishermen and observing fishing vessels and gears.
+During their meeting with H.E Minister of Agriculture, Mr. Abbas Mortada, the experts discussed the strategic solutions for preserving and sustaining fisheries resources in light of the challenges facing the sector. The minister stressed the importance of strengthening the capacities of the Lebanese fishermen in addition to applying the necessary standards and conditions for protecting and sustaining the fisheries sector.
+The experts also met with the Director-General of the Ministry of Agriculture, Director General of the Marine and Land Transport at the Ministry of Public Works and Transport, the Commander of the Lebanese Navy at Beirut Naval Base, staff from the Department of Fisheries and Wildlife (DFW) at the Ministry of Agriculture and other Ministry relevant staff, UN agencies, donors and NGOs.
+In this context, the fishing experts kicked off the work for undertaking the fishing vessel census by training the enumerators and data collectors of the Ministry of Agriculture on survey methodology and details of an elaborated questionnaire. Following the training, they went to the Dora Fishing Port and tested its application.
+The last fishing vessel census was performed in 2004. The forthcoming census questionnaire compiles about 16 sections related to the fishermen, vessel and its requisites and the gears and equipment used in the fishing activities.
+At the request of the Ministry of Agriculture, and through FAO’s technical cooperation programme, FAO Lebanon launched in September 2019 a project which will provide the Lebanese Government the technical assistance to accurately assess the fishing fleet and its related requisites. For this purpose, a national census will be conducted.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:08.632550+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Green Plan staff trained on orchard establishment</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Green-Plan-staff-trained-on-orchard-establishment/en</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Green Plan staff trained on orchard establishment
+“The establishment of an orchard deserves planning and preparation and the seedlings need to be carefully selected to ensure good production,” said Charbel Hobeika, a technical expert leading a training organized by the Food and Agriculture Organization of the United Nations in Lebanon.
+Under the framework of the FAO project “Promotion of Agricultural Livelihoods and Employment through Investment in Land Reclamation and Water Reservoirs” funded by the Kingdom of the Netherlands, the training took place in December 2019 and January 2020 as part of a capacity-building exercise for the benefit of the Green Plan (GP) staff. In fact, the GP staff are in direct contact with GP beneficiaries investing in land reclamation, 90% of whom opt to plant fruit trees on their lands. Eleven men and nine women participants were trained on orchard establishment, varieties and rootstocks selection for a number of main fruit species planted in Lebanon, in addition to estimating the costs and revenues of such investments.
+In order to sustain rural communities and to reduce rural exodus, the Lebanese Ministry of Agriculture (MoA) through its affiliated Green Plan (GP), launched in 1963 a demand-driven support program allowing farmers to benefit from subsidies to invest in agriculture infrastructure including land reclamation for agriculture, soil and water conservation, planting of fruit trees, and other complementary works. The GP program has empowered a large number of farmers to invest in reclaiming their abandoned lands or rehabilitating/upgrading low-productivity lands.
+“The training enabled us to acquire new concepts we didn’t learn in the technical school”, said Samah Badra from the North Bekaa office. For engineer Bassam Harb, the training is important to his work as it highlights important tips and guidelines to support the farmers.
+The trainer shared practical demonstrations of orchards newly established using intensive systems, and of training and pruning of trees, removing weak crotch angles and tip-pruning long branches throughout the seasons in an interesting video. “The trainer is multidisciplinary. The training is well prepared and is based on demand from GP” said Georges Chemaly, Head of Mount Lebanon One regional office, adding “we can now better speak the farmer’s language”.
+“I am eager to take part in the demonstration field days,” said Zeinab Zahraman, from the North Lebanon regional office who found the training very useful.
+This training session will be complemented in January and February 2020 with a tour of orchards where different orchards are newly established and a number of varieties are grown.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:15.494620+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FAO Concludes its Regional Conference on Improving Water Productivity in Agriculture Showcasing Innovation</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-Concludes-its-Regional-Conference-on-Improving-Water-Productivity-in-Agriculture-Showcasing-Innovation/en</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>FAO Concludes its Regional Conference on Improving Water Productivity in Agriculture Showcasing Innovation
+©FAOSNE Field trip to the pilot site in Kairouan
+Tunis/Cairo 10 December 2019
+With innovative ideas from young Tunisians, the Food and Agriculture Organization of the United Nations (FAO) concluded in Tunisia the Regional Conference on Improving Water Productivity in Agriculture in the Near East and North Africa.
+Rich in scientific discussion and specialized concurrent training sessions, the conference benefited from the expertise of participants from 23 countries and served as a platform for exchanging knowledge and best practices.
+The Collaborative Platform on Water Productivity developed within the regional Initiative on Water Scarcity and other advanced products introduced by FAO and its partners at the market place allowed participants to have first-hand experience of these tools and their benefits.
+Discussions and training
+Supported by the FAO regional project “Implementing the 2030 Agenda on Water Efficiency, Productivity and Sustainability in the Near East and North Africa Countries,” funded by the Swedish International Development Cooperation Agency (SIDA), this conference allowed experts to debate how improvements in Water Productivity can reinforce agricultural sustainability, promote economic development, maintain social stability and protect the environment in rural areas and cities.
+In order to maximize the impact on the participants, FAO organized a series of training sessions on the mapping of soil salinity, the Wapor application for monitoring water productivity and using satellite imagery and remote sensing, and on water accounting, which is an important component for water resource planning and management. There was also a high-level meeting of the Aquacore group to monitor this widely-used agricultural water productivity simulation tool.
+The conference included a field visit to Kairouan, in Northern Tunisia, one of the pilot sites of the project funded by Sweden to support the implementation of a water accounting exercise, an evaluation of water productivity, and four farmer field schools around local olive production.
+World Soil Day
+On 5 December, the conference joined in celebrating World Soil Day with a combination of artistic expression and serious talk: Young Tunisian talents expressed their concerns and ambitions in a mime play and with thematic songs, echoed in the speech of Mr. Philippe Ankers, FAO Sub-Regional Coordinator for North Africa, who emphasized the theme of this day: “Stop soil erosion to save our future.”
+He recalled the multiple devastating effects of erosion, described in the Status of World Soil Resources report, as “the most serious global threat to proper soil management.”
+Hackathon winners
+The conference witnessed another stirring moment with the announcement of the winning groups of young Tunisian university students who participated in a “Hackathon” to develop innovative technological solutions to water productivity issues. The “Hackathon” was launched on 1 October 2019 at the Technopark of the University of Manouba in Tunis during a seminar on “Smart Irrigation” held there in partnership with FAO.
+The “Hackathon” challenged the students to create innovative software solutions and applications to address any of these three challenges: improving agricultural production per volume of water, improving water use efficiency, and developing communication tools to improve water productivity.
+Teams were selected from seven Tunisian institutes: The National Institute of Applied Science and Technology; the National Agronomic Institute of Tunisia; the High Institute of Informatics; the Institute of Statistics and Information Analysis; the National Institute of Computer Science; the Institute of Commerce of Tunis and the Institute of the Digital Economy.
+Hackathon participants had the opportunity to develop their ideas at the co-working space Al-Gazala Incubator Park of the Manouba Technopark. The results of their efforts were judged by a jury of experts, including FAO officers and startup managers. The winning ideas included robots and applications, showcasing innovation and a sense of responsibility among the young Tunisians.
+While the Scientific Committee of the conference is working on drafting the final recommendations and the associated action plans, this conference will have a positive impact on improving water productivity in the Near East and North Africa region. It will also benefit the Regional Initiative on Water Scarcity and help address the most urgent challenges: food security and water security for sustainable economic and social development in a context of water scarcity.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:22.085934+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Korea supports the implementation of a new FAO project in Anjar</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Korea-supports-the-implementation-of-a-new-FAO-project-in-Anjar/en</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Korea supports the implementation of a new FAO project in Anjar
+Three Korean experts from the Forest Research Institute in the Republic of Korea visited Lebanon between December 2 and December 5,2019.
+Their first destination was Anjar in the Bekaa where they held fruitful meetings with local actors and authorities. The experts also visited the Cedars of God in Besharre, North Lebanon in addition to some sites affected by the latest fires in the lower Chouf, Mount Lebanon.
+The objective of the visit is to know more about the Lebanese forests within the context of the latest collaboration between FAO and the Ministry of Foreign Affairs of the Republic of Korea.
+On November 18, 2019, H.E. Young-Dae Kwon, Ambassador of the Republic of Korea in Lebanon, and Dr. Maurice Saade, FAO Representative in Lebanon, signed a Memorandum of Understanding for the implementation of the FAO-led project “Enhancing the Resilience of Vulnerable Refugee Communities through Cash-for-Work”. The project will be implemented in collaboration with the Association for Forests, Development and Conversation (AFDC) and the Lebanon Reforestation Initiative (LRI).
+The Ministry of Foreign Affairs of the Republic of Korea contributed with the amount of USD 500 000 to the project that aims at enhancing the livelihoods of vulnerable Lebanese and displaced Syrians through labor-intensive reforestation and forest management activities in the municipality of Anjar, Bekaa.
+In collaboration with the Ministry of the Agriculture (MoA) and the Municipality of Anjar, the project will implement reforestation and forest management activities over an area of 95 ha in Anjar. This will be done through recruiting Lebanese and displaced Syrians laborers from the localities of Anjar, Kfarzabad and Qab Elias in the Bekaa governorate.
+The laborers will receive training on reforestation and forest management techniques. By doing so, the project will be creating short-term jobs for the displaced and for local communities while contributing to sustainable forest management, creation of green belts and wildfire prevention.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:31.167550+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FAO Lebanon and partners have initiated reforestation and afforestation activities all over Lebanon for the 2019 campaign</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/FAO-Lebanon-and-partners-have-initiated-reforestation-and-afforestation-activities-all-over-Lebanon-for-the-2019-campaign-/en</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>FAO Lebanon and partners have initiated reforestation and afforestation activities all over Lebanon for the 2019 campaign
+The “Smart Adaptation of Forest Landscapes in Mountain Areas” (SALMA) FAO- led project, funded by the Global Environmental Facility (GEF), kicked off reforestation and afforestation activities in Lebanon for this year. In collaboration with the Lebanese Ministry of Agriculture, and in partnership with municipalities and NGOs, the activities started during the first week of November 2019 by planting around 9,000 seedlings in different parts of the country.
+On November 5, 2019, SHEILD NGO planted 3,500 seedlings out of 36,000 planned in Taybeh, Nabatieh, in partnership with Taybeh municipality and the World Food Programme (WFP). SHEILD aims at planting 5,000 seedlings per week till the end of 2019 depending on weather conditions.
+“SHEILD and FAO are working together to restore and compensate for what has been lost of green areas of Lebanon. This could be the first step in the thousand miles journey to get back the green Lebanon”, said Ayman Alroz, SHEILD Executive Director.
+Jouzour Loubnan NGO planted 3,000 cedar seedlings out of 16,650 to be planted over an area of 20 hectares in Jaj Cedars Nature Reserve. The activity started in November 2019 and will continue till October 2021. The NGO has already worked in close collaboration with the local authorities and municipalities of the Mount Lebanon region. According to Jouzour Loubnan, these initiatives are a great success, have a positive impact and trigger a deep sense of gratitude from the local community.
+In the Jurd of Keserouan, the Lebanon Reforestation Initiative (LRI) planted 2,000 seedlings of Cedrus libani, Juniperus exelca, Pyrus syriaca and other species.
+In Keserouan, LRI adopted an integrated land use planning approach taking into consideration many factors and land users in the plot including shepherds, hunters, and tour operators.
+Juan Hobeiche, Head of the Keserouan Union of Municipalities, participated in the afforestation activity implemented by LRI. He highlighted its benefits and the importance of the conservation and sustainable management of the forests. “Afforestation and reforestation have a socio-cultural impact as they push citizens to be attached to their home country and land” Hobeiche said adding: “We are trying to get students, scouts, and NGOs involved in such activities. We will also involve the staff of the Union of Municipalities in the planting.”
+The SALMA project will continue the reforestation and afforestation activities throughout the year in partnership with several NGOs and municipalities in Lebanon. In South Lebanon, FAO will be working with the Association for Forests, Development and Conversation (AFDC) and AMWAJ of the environment and SHEILD. In North Lebanon, the activities will be carried out in partnership with Horsh Ehden Nature Reserve and the Committee of Cedar Forest Friends. In the Bekaa, Cooperation Without Borders for Tailored Development (CWB), the Lebanese Organization for Studies and Training (LOST) and LRI will be implementing the activities in close coordination with municipalities and local stakeholders; while Oaks &amp; Cedars will be planting on the slopes of Hammana.
+Reforestation and afforestation efforts are taking place in the framework of FAO’s ongoing support to “The 40 Million Trees Pogramme” launched by the Ministry of Agriculture in 2012. This programme aims at increasing the Lebanese forest cover from 13 percent to 20 percent by 2030 through planting 70,000 ha (40 million trees).
+Through the SALMA project, FAO is also promoting a climate resilient and participatory sustainable forest management approach aiming at maintaining and restoring connectivity within ecological corridors, while improving the income of vulnerable households living in mountainous areas.
+It is worth noting that the FAO GEF-funded SALMA Project (Smart Adaptation of Forest Landscapes in Mountain Areas) is the largest FAO forestry project in the Near East Region.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:37.906823+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High-Level Technical Workshop tackles the challenges and opportunities for Lebanon’s Agriculture</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/High-Level-Technical-Workshop-tackles-the-challenges-and-opportunities-for-Lebanon-s-Agriculture/en</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>High-Level Technical Workshop tackles the challenges and opportunities for Lebanon’s Agriculture
+Agriculture plays a vital role in the Lebanese economy. However, the agricultural sector is facing significant challenges. To tackle these challenges and address the possible opportunities for Lebanon’s agriculture, the Ministry of Agriculture of Lebanon, in partnership with the Food and Agriculture Organization of the United Nations (FAO) and the World Bank organized, under the patronage of the President of the Council of Ministers, a High-level technical workshop titled “Transforming Lebanon’s Agriculture: Challenges and Opportunities” on October 4, 2019 at the Grand Serail.
+Opening speeches of H.E. Dr. Hassan Lakiss, Minister of Agriculture, Dr. Maurice Saade, FAO Representative in Lebanon, Mr. Saroj Kumar Jha, Regional Director of the World Bank and Ms. Wafaa Dikah Hamze, Former Minister &amp; Chairperson of the organizing committee of workshop, stressed on the need to support the agriculture sector in Lebanon and make it a priority.
+The workshop aimed at initiating the dialogue at policy-making level to review and develop the agricultural policies and pave the way forward for a clear vision of the Lebanese agriculture and to its better placement in the new government economic vision. It focused on discussing pertinent global best practices, to inform future investments and actions, to promote inclusive agriculture transformation, enhance innovation in agriculture and foster higher competitiveness of Lebanese agricultural products.
+The Ministry of Agriculture in Lebanon has recently requested the support of the Food and Agriculture Organization of the United Nations (FAO) and the World Bank to initiate a wide-ranging review for the development of the agriculture sector in Lebanon. This review will assist the Ministry in the formulation of a new Agriculture Strategy (2021-2025), which is expected to be completed by mid-2020 and will identify priority areas for action.
+The workshop was concluded by a panel discussion moderated by Dr. Mouin Hamze, Secretary General of the National Council for Scientific Research. In the presence of H.E Mr. Saad Hariri, H.E. Dr. Hassan Lakiss, Minister of Agriculture, H.E. Mr. Mansour Bteich, Minister of Economy and Trade, H.E. Mr. Ali Hassan Khalil, Minister of Finance and Dr. Nadim Munla, Prime Minister’s Adviser discussed the role of agriculture in the future economic vision of Lebanon.
+“Agriculture is an essential sector, and it is important that we maintain that vitality,” said the Prime Minister during the workshop’s concluding session.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:44.397339+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Technical Agriculture Education, Entry Point into Green Jobs for Youth</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Technical-Agriculture-Education-Entry-Point-into-Green-Jobs-for-Youth/en</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Technical Agriculture Education, Entry Point into Green Jobs for Youth
+“I advise youth to enroll in the Technical Agriculture Schools as they will learn a lot and gain new experiences to become ready to join the labor market”, said Batoul Kanj, a displaced Syrian student who flew with her family from her country and found an opportunity for studying at one of the Technical Agriculture Schools. She now plans to open a flower shop where she applies all the techniques she has learned in the school.
+Batoul benefited from the “Upgrading the Technical Agriculture Education System in Lebanon” project lead by the Food and Agriculture Organization of the United Nations (FAO), funded by the Kingdom of Netherlands and implemented in partnership with the Ministry of Agriculture, UNICEF, ILO and AVSI.
+The project works on enhancing the employability of young Lebanese and displaced Syrians and other refugees in Lebanon. It offers them the opportunity of acquiring the necessary technical skills to access improved career opportunities in agriculture and agribusiness in Lebanon or in Syria upon their return, accordingly. It also works on the efficiency of the agriculture education system in Lebanon to support more youth. This is done by improving the agricultural capacity development and creating entry points into green jobs.
+“I started my vocational training two years ago in the Agricultural Technical School. Now, I am responsible of the quality of the whole potato production process” proudly explains Ahmad Tarshishi, a student at one of the Technical Agricultural Schools. Just like Ahmad, Mohammad Nasrallah, a Technical Agriculture School graduate had the chance to learn agricultural techniques and to specialize in beekeeping. “I encourage each person who has a passion for agriculture to enroll in Agricultural Technical Schools” he said.
+In this context, the FAO-led project works on increasing the enrollment of the youth to the technical agriculture and vocational programs of the Lebanese Ministry of Agriculture.
+In order to ensure a better outreach to the youth and the rural community, FAO in partnership with UNICEF developed in September 2019 a social media campaign and a national TV campaign for its agricultural TVET program.
+The messages shared on social media platforms inspired young people in Lebanon to join the program. As a reaction to the posts, youth commented on the social media posts asking about the nearest school in order to register.
+In one of the movies shared on social media, Sari Bou Karroum, Agriculture School Alumni encouraged the youth to enroll in the schools saying : “ Education helps you develop and leverage your skills. You cannot improve yourself without education… It helps you have a better-quality product of your farm business.”
+Sari and many other youth shared their success stories, testimonies and experiences through the “Upgrading the Technical Agriculture Education System in Lebanon” project.
+The social media campaign that was widely shared, was an advocacy tool to show the real challenges youth in Lebanon are facing in this field. It also reflected the efforts of the government, the Food and Agriculture Organization (FAO) and its UN partner agencies to address these challenges.
+The campaign highlighted the importance of the technical education in agriculture and raised awareness on the employment horizons in Lebanon for youth in agriculture. It encouraged them to make a difference in this sector, having leadership role to economic growth in the country, at personal and national levels.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:50.973964+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Assessment of Fishing Fleet and its Related Gears in Lebanon</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Assessment-of-Fishing-Fleet-and-its-Related-Gears-in-Lebanon-/en</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Assessment of Fishing Fleet and its Related Gears in Lebanon
+Under the patronage of H.E The Minister of Agriculture, Dr. Hassan Lakiss, the Food and Agriculture Organization of the United Nations (FAO) and the Ministry of Agriculture (MoA) in Lebanon, held an inception workshop at the Ministry of Agriculture on August 26, 2019 to launch the national project related to the assessment of the fishing fleet and its related gears in Lebanon.
+The launch was attended by Mr. Ibrahim Al Hawi representing H.E the Minister of Agriculture and the Assistant of the FAO Representative in Lebanon, Ms. Solange Matta-Saade. The Director of Natural Resources and Rural Development department at the Ministry of Agriculture, Dr. Chadi Mhanna, also took part in the launch event along with the Senior Fisheries Officer in FAO Regional Office for the Near East and North Africa in Cairo, Dr. Haydar Fersoy, and representative of the General Fisheries Commission for the Mediterranean, Mr. Samir Majdalani. Guests included participants from various departments of the Lebanese Ministry of Agriculture, representatives from the Ministry of Public Works, institutions, universities and concerned stakeholders.
+At the request of the Ministry of Agriculture, the project, through FAO’s technical cooperation programme, will provide, for the Lebanese Government, the technical assistance to accurately assess the fishing fleet, the fishing gears used and related activities. For this purpose, a national census will be conducted for the fishing fleet and its related gears. The project is expected to result in responsible fishing sustained improved livelihoods of fishers through good quality and quantity of landed fish.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:43:57.149372+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FAO and partners join efforts to adapt to climatic change in the Near East and North Africa</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-and-partners-join-efforts-to-adapt-to-climatic-change-in-the-Near-East-and-North-Africa/en</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>FAO and partners join efforts to adapt to climatic change in the Near East and North Africa
+9 September 2019, Cairo – The Food and Agriculture Organization of the United Nations today hosted a workshop in Cairo to enhance the technical capacity to climate change adaptation in the Near East and North Africa (NENA) countries’ agriculture sector.
+Around 100 participants from 14 member countries in the region, delegates from partner entities and regional media attended the opening session, in which Pablo Vieira, Global Director of NDC Partnership, Mohamed Abd-Elaty, Minister of Water resources and irrigation, and Saad Nassar, Advisor of the Minister of Agriculture and Land Reclamation delivered statements, in addition to the opening remarks by Abdessalam OuldAhmed, Assistant Director-General and Regional Representative for the NENA region. Yasmine Fouad, Minister of Environment in Egypt, also delivered a statement highlighting the importance of climate change, salinity and biodiversity agendas in Egypt.
+Throughout a three days program, the workshop is offering a knowledge-sharing platform through bringing in all stakeholders together towards identifying innovative and effective interventions to address the impacts of climate change across the region, in fulfilment of the Paris Agreement agenda that was signed in 2015 by developed and developing countries; in a commitment to addressing climate change issues.
+The workshop will provide an opportunity to enhance partnership and mobilise resources for implementing the Nationally Determined Contributions (NDCs) commitments in the region.
+Adapting to a global threat
+Climate change is widely recognised as a global threat - to humans, a wide range of species and the environment. The importance of climate change adaptation has been highlighted at a global level, including under the Paris Agreement and the Sustainable Development Goals (SDGs).
+In his opening statement, Abdessalam OuldAhmed, Assistant Director-General and Regional Representative for the NENA region, explained how FAO supports its member states to adapt and mitigate climate change, working in close collaboration with UNFCCC and other partners. “FAO participates in the NDC Partnership’s work as an implementing partner through its country, sub-regional and regional offices, with the support provided by a dedicated team in its Headquarters in Rome, to ensure that the importance of the agricultural sectors is reflected in countries’ NDC implementation strategies and plans”, he added.
+Besides, FAO facilitates the Thematic Working Group (TWG) on Agriculture, Food Security and Land Use under the umbrella of the NDC Partnership. The TWG aims at fostering countries’ climate change action in the agricultural sectors through knowledge exchange and peer-to-peer learning activities.
+The most vulnerable region to Climatic change
+According to the global and regional FAO assessments, NENA is the most vulnerable region to climatic change, in the world. The Region is predicted to become even hotter and dryer than ever. Sea level rise of about 0.1 to 0.3 meters is also expected by the year 2050, augmenting seawater intrusion to coastal groundwater resources. FAO’s recent study on the impact of climate change on the different farming systems and the livelihoods in the Region showed that a large segment of the region’s population, particularly those depending on small scale rain-fed agriculture, will be at great risk. The report indicated that there is “high confidence” that many oases of North Africa and the Arabian Peninsula are vulnerable to climate change. Consequently, the anticipated impacts of climate change will pose additional stress on food production systems under pressure to satisfy the food needs of rapidly growing populations.
+Between 1998 and 2012, the drought that hit the eastern Mediterranean (Jordan, Lebanon, Palestine and Syria was the worst in the past nine centuries. The recent drought in the winter of 2015-16 affected all North African countries, causing a significant reduction in grain production in Algeria, Morocco and Tunisia.
+FAO, the Paris Agreement and NDC
+The Paris Agreement, which was signed in 2015 by 196 Parties, aimed at limiting global warming in an attempt to adapt to the impacts of climate change, and amplify climate resilience and low greenhouse gas emissions development, in a manner that does not threaten food production in particular. The agreement objectives rely on the Nationally Determined Contributions (NDCs) those signing parties submitted to the United Nations Framework Convention on Climate Change (UNFCCC).
+About 90 percent of the countries' NDCs refer to FAO analysis of the agriculture sectors in its strategies’ implementation. The FAO publication, ‘The agricultural sectors in nationally determined contributions (NDCs): Priority areas for international support', identifies areas of intervention that apply to all areas of FAO’s work on climate change. Its sequel, Turning Nationally Determined Contributions into action, outlines the related support FAO has to offer.
+Contact
+FAO Regional Communication Office for the Near East and North Africa</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:03.567400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>International Plant Protection Convention (IPPC) 2019 Regional Workshops is in Beirut</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/International-Plant-Protection-Convention-(IPPC)-2019-Regional-Workshops-is-in-Beirut/en</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>International Plant Protection Convention (IPPC) 2019 Regional Workshops is in Beirut
+2 September 2019, Beirut - National contact points of the International Plant Protection Convention (IPPC) and agricultural experts from Near East and North Africa Region countries are meeting in Beirut for a regional workshop in Beirut from 2 to 6 September 2019. Participants will prepare regional positions on international phytosanitary standards, develop phytosanitary capacity for preventing the entry and establishment of invasive plant pests and share plant health best practices.
+Under the auspices of H.E the Minister of Agriculture, Dr. Hassan Lakiss, the workshop is organized by the IPPC Secretariat, in cooperation with the Lebanese Ministry of Agriculture and the UN’s Food and Agriculture Organization of and the Near East Plant Protection Organization (NEPPO). The meeting in Lebanon is one of seven IPPC annual regional workshops hosted around the world in 2019 under the theme “Plant Health and Capacity Development”.
+During the opening session held today, Mr. Maurice Saade, FAO Representative in Lebanon mentioned that the annual regional workshop represents an important technical forum that gathers all regional plan protection organizations. “It enables the discussion and exchange of information and knowledge about different issues and pests of interest for the region”, he said.
+Mrs. Sylvana Gerges representing the Lebanese Ministry of Agriculture said that the ministry is keen on abiding by the International Standards For Phytosanitary Measures (ISPMs) and cooperating with Arab and NENA countries for safe trade facilitation. “The Ministry also works through this cooperation on promoting phytosanitary capacity building in order to counter the spread of transboundary pests and face its emerging challenges”, she added. “This event aims to raise awareness of the importance of developing the capacity of staff, institutions and systems at the national level to improve plant health,” said Mr. Jingyuan Xia, IPPC Secretary. He emphasized that phytosanitary capacity evaluations (PCEs) play an important role in supporting national phytosanitary capacity and encouraged participants to discuss this issue.
+“IPPC annual meeting strengthens the technical networking among plant protection experts, IPPC contact points, NEPPO and FAO officers for addressing emerging plant pests concern in the region” said Mr. Thaer Yaseen, Regional Plant Protection officer for Near East and North Africa Region and North Africa (FAO-RNE). He added, this event is improving of the information sharing and regional collaboration in prevention and control of plant pests. Mr. Mekki Chouibani, Executive Director of the Near East Plant Organization (NEPPO) explained that at the regional level, the NEPPO constitutes a special regional forum for the support an promotion of coordination and consultation as well as ongoing cooperation amongst member states in the phytosanitary field in view of strengthening necessary measures, especially the preventing ones to avoid the spread of dangerous agricultural pest from one country to the other.
+The workshop will also highlight preparations for the International Year of Plant Health 2020 and encourage participants to discuss how to promote it in their countries. In the words of Francisco Javier Trujillo Arriaga, CPM Chairperson: “The phytosanitary community is facing increasing challenges from ever-expanding trade to climate change. The IYPH is expected to put plant health and protection high on the policy agenda and increase the public’s awareness of its importance in achieving the Sustainable Development Goals.”
+The International Plant Protection Convention is an international treaty established in 1952 whose Secretariat is hosted by FAO. Its mission is to protect the world’s plant resources by preventing the introduction and spread of harmful pests.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:10.115648+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FAO organizes regional workshop on Water Hyacinth management and control in Al Nahr Al Kabir River</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-organizes-regional-workshop-on-Water-Hyacinth-management-and-control-in-Al-Nahr-Al-Kabir-River/en</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>FAO organizes regional workshop on Water Hyacinth management and control in Al Nahr Al Kabir River
+Tripoli, 27 June 2019 -
+About 25 plant protection, bio-control and water management specialists from Syria and Lebanon participated in a workshop held by the Food and Agriculture Organization of the United Nations (FAO) in the cities of Tripoli and Al Abdeh in northern Lebanon to identify methods used to control water hyacinth, which has widely spread in the Wadi al Kabir River for years. The four-day workshop was held in cooperation with the Lebanese Ministry of Agriculture, the Lebanese Ministry of Energy and Water, and the Syrian Ministry of Agriculture and Agrarian Reform. The aim was to share Egypt’s successful experience in controlling the weed through biological means.
+Representatives of the Lebanese and Syrian ministries discussed the danger of the spread of water hyacinth in streams and water bodies and the national efforts being made in both countries to control the spread of this harmful weed.
+Dr. Thaer Yaseen, Plant Protection Officer at the FAO Near East and North Africa Office in Cairo, noted that water hyacinth endangers the livelihoods of many farmers and fishermen who depend on the Al Nahr Al Kabir River for their living. He said the wide and rapid growth of the weed blocked irrigation channels and pump pipes. The weed also causes the loss of huge amounts of water as a result of evaporation and erosion, disrupts river navigation, and hampers fishing operations. It also has a negative impact on aquatic organisms as it prevents sunlight from the reaching the river.
+The FAO response came after the governments of Syria and Lebanon requested the UN agency’s help to manage water hyacinth and reduce its harmful effects. FAO brought in biological control experts to transfer the successful Egyptian experience in controlling the weed through biological agents.
+Dr. Yahya Fayyad, a bio-control expert at the Plant Protection Research Institute, Egypt's Agricultural Research Center, explained that it is possible to control the weed using two types of weevils that feed on water hyacinth. He said Egypt brought the two types from the original home of water hyacinth in the Amazon River Basin in South America in the seventies and conducted many experiments to make sure the insects did not feed on any other plants. Studies were also made on the lifecycles of those insects and their ability to control water hyacinth.
+“Based on the results of those studies, a number of those insects were released in many water bodies in Egypt, such as the lakes of Mariout and Idku, between 2000 and 2009, and the results showed that the insects were able to reduce water hyacinth by 70- 95%,” he said.
+In addition to theoretical lectures, the workshop included field visits to the sites in Nahr Al Kabir River basin on the Lebanese-Syrian border where the weed is spread to train the participants on ways to deal with the herb, evaluate its spread, and identify the different parts of the plant and ways to examine them to find the biological enemies.
+The participants explained that mechanical control methods over the past years did not yield the desired results. The population in the river basin area increasingly complain about the damage that the weed causes to their livelihoods. Biological control specialists from the Syrian side reviewed successful experiments to eradicate the weed from some water bodies in Lattakia as well as the national plans to establish laboratories to produce biological enemies of the weed in Tartous Governorate. They also explained some initial experiments that were conducted by releasing biological enemies in Mahrada Dam (on the Orintos) in Hama Governorate.
+Discussions continued during the four days of the workshop to come up with a joint action plan that would allow for effective measures to control the weed in Al Nahr Al Kabir. The most important points in the plan of action is the need to accelerate the establishment of centers for the production of pathogens in Tartous in Syria as well as centers for receiving and preserving these agents in the province of Akkar in northern Lebanon. The action plan also stressed the need to use modern remote and satellite imaging techniques to follow the weed and the impact of the biological control agents. It also encourages full coordination among the different ministries within and between countries so that control measures can succeed.
+Water hyacinth is one of the most dangerous invasive plants in the world, as it was able to spread from its place of origin in South America to all other continents with the exception of The Arctic Ocean. The weed’s capacity to double its population in 10-12 days makes it the fastest growing plant on Earth. These plants absorb billions of cubic meters of water, resulting in water scarcity in many areas, and causing the death of aquatic organisms in rivers and lakes.
+Many experiments have shown that these plants are of no use because they absorb toxic heavy metals, which in turn may be transmitted to animals feeding on them or even to the land in which they are buried. Moreover, the roots of the water hyacinth contain many intermediate hosts of parasites, such as snails that cause Schistosomiasis, and can be a breeding habitat for female mosquitoes. The larvae of mosquitoes then stick to the roots of the plant triggering the spread of mosquitoes and mosquito-borne diseases.
+The beauty of water hyacinth flowers led to its introduction into Egypt during the reign of Mohammed Ali to decorate water bodies around the royal palaces, but the plant spread out of control causing a lot of problems until it was finally controlled after 2000 by means of planting certain species of weevil that were imported from South America, feeding exclusively on water hyacinth and thus destroying its capacity to reproduce and spread.
+The participants in the workshop made recommendations to manage the harmful weed, and these were discussed with the concerned experts. At the end of the workshop, a joint program to control water hyacinth in Al Nahr Al Kabir River will be worked out.
+The workshop also helped the participants develop control programs for a number of rivers infested with water hyacinth in Syria. The workshop also came up with important recommendations regarding the activation of laboratories to produce biological enemies in Tartus in Syria and the cooperation between the two countries on the use of these agents and on continuous monitoring of the weed in the river to remove it at an early stage before it covers the water body.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:16.066027+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>The Near East and North Africa region needs to step up its efforts to end hunger by 2030</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/The-Near-East-and-North-Africa-region-needs-to-step-up-its-efforts-to-end-hunger-by-2030/en</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>The Near East and North Africa region needs to step up its efforts to end hunger by 2030
+Children in their school’s vegetable garden, Syria. FAO/Zaki Khozam
+Rome, 27 June 2019 – Countries in the Arab region need to set up policies supporting local food production and improve their governance of natural resources if hunger is to be eradicated from the Near East and North Africa by 2030.
+This was FAO Director-General José Graziano da Silva’s message to participants at The Arab Region towards Zero Hunger: Challenge and Opportunities event on the sidelines of the 41st Session of the FAO Conference.
+“No one is questioning the lack of natural resources in the region and that the main issue is water scarcity. But when you look at how water is used, you see a lack of good governance,” the FAO chief said.
+He pointed out that many countries in the region – which has a population of 400 million - do not have a central authority to manage the use of water and of other resources.
+“Lack of policies and good governance make the problems of the Near East and North Africa region worse, Graziano da Silva said and asked countries in the region to consider setting up a “central authority” to better manage the use of water.
+The FAO Director-General also urged countries to put more emphasis on stimulating local food production, pointing out that the issue of obesity – a growing concern in the region – is also due to a reliance on importing cheap and unhealthy food.
+The Near East and North Africa region suffered a serious setback in its Zero Hunger progress
+The region has been grappling over the past years with many challenges that have consequently led to a serious setback in its progress towards Zero Hunger.
+These include the increasingly unsustainable use of already scarce or dwindling natural resources, especially water, rising hunger and malnutrition, protracted socio-political crises in several countries, the impacts of climate change and economic slowdown.
+A recent food insecurity analysis shows that 52 million people suffer from hunger in the region’s 18 countries. But whilst hunger – driven mainly by conflict - is on the rise, so are overweight and obesity, with nearly one in three adults being obese.
+“While all efforts to boost agricultural productivity need to be made, the countries of the region also need to look beyond production to ensure safe and stable access to food for all its people,” said Abdessalam Ould Ahmed, FAO’s Assistant Director-General and Regional Representative for the Near East and North Africa.
+To achieve that, Ould Ahmed put forward the following: end conflict and refocus attention and resources on the Sustainable Development Goals (SDGs), particularly on SDG2 – Zero Hunger; achieve greater complementarity between policies on food security, agriculture, trade and water; invest more in initiatives that address water scarcity and climate change; reduce food loss and waste; and shift to healthier and more nutrition diets with less sugar and fat and more fruits, vegetables, and fish.
+Ould Ahmed also urged participants to build on successful Zero Hunger initiatives of several countries and not let regional challenges outshine some countries’ progress in ending hunger.
+Accelerating action on ending hunger
+Several experiences and visions were shared at the side event as a spur to accelerate action on ending hunger in the region.
+In a video message to the event at FAO, Ahmed Aboul Gheit, Secretary-General, League of Arab States pointed out the need to better understand and elaborate on the indicators of SDG2 to chart the region’s progress towards reaching the goal. “FAO is working tremendously hard to put the fight against hunger into the context of the future. This vision will be needed to face the challenges of climate change and address other environmental issues," he added.
+Ahmed bin Nasser Al Bakri, Oman’s Undersecretary of the Ministry of Agriculture and Fisheries Wealth highlighted the need to tackle the greatest challenges facing agriculture in the region – “the common burden of water scarcity, land degradation and climate change”.
+“We need to face the water challenge through a new perspective. For this reason, we need to develop new technologies and appropriate policies and choose the right kind of investment. The same applies to land degradation, which has become a major burden on the sustainability of agriculture in many of our countries,” Nasser Al Bakri added.
+Darine El Khatib, FAO Special Goodwill Ambassador for Zero Hunger for the Near East and North Africa stressed how,
+“everyone can play a role in eliminating hunger, and each of us can contribute to this goal in different ways. The media can play a leading role in this if used properly,” she said, adding that raising awareness on how not to waste food, or how to save energy and recycle waste can help boost everyone’s role in ending hunger.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:17.693806+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FAO develops a roadmap framework for use of non-conventional water resources in Agri-aquaculture</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-develops-a-roadmap-framework-for-use-of-non-conventional-water-resources-in-Agri-aquaculture/en</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>FAO develops a roadmap framework for use of non-conventional water resources in Agri-aquaculture
+Cairo, 25 June, 2019 - The Food and Agriculture Organization of the United Nations (FAO), today held a regional workshop as part of the project “Use of Non-conventional water in Agriculture in Support of Sustainable Agri-aquaculture Development in Desert and Arid Lands in the Near East and North Africa region, the Cases of Algeria, Egypt and Oman, to share project outcomes with experts and develop a roadmap framework for scaling up in the NENA region.
+This workshop is organized under the FAO Regional Initiative on Water Scarcity for the Near East and North Africa in collaboration with FAO HQs and respective national authorities of the beneficiary countries of the project. And other participating countries experts from Jordan, Lebanon, Mauritania Saudi Arabia, Palestine and Sudan,
+In his opening speech opening, Mr. Serge Nakouzi, FAO Deputy Regional Representative, for the Near East and North Africa, highlighted The constant growth of the human population and the continuous exploitation for land and water resources particularly in arid lands, will require the application of new strategies to ensure adequate food production by populations living in remote and isolated areas. The integration of aquaculture with agriculture is becoming progressively more attractive in areas where water is a limited resource.
+“In this regard, integrated agri-aquaculture systems create value to both farm business, particularly of small-scale farm household in rural areas, and the consumer while contributing to less water usage. Therefore, these type of integrated farming systems can be attractive for youth and create new employment opportunities in areas affected by chronic migration of people towards cities or abroad” Nakouzi said.
+As part of the project, this workshop has been designed to share the knowledge and develop a regional roadmap to identify areas where collaboration and progress may be made.
+“The expected key outcomes of the workshop will include improved knowledge on the status of practices of integrated agri-aquaculture farming in NENA region, shared experiences, lessons learned best practices and new techniques in the use of non-conventional water in integrated agri-aquaculture farming in NENA region, and finely a regional non-conventional water use roadmap framework for development of integrated agri-aquaculture farming” Haydar Fersoy, Senior Fishery and Aquaculture Officer, FAORNE said.
+The project was launched in 2017 under FAO Regional Initiative on Water Scarcity for the Near East and North Africa. The main objective of this study was to analyse the use of non-conventional sources of water taking the three selected countries as case study, for use in integrated agriculture-aquaculture systems in the arid environments prevalent in the NENA region, as a means to produce more food per unit of water used, as part of increased development for aquaculture in the region.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:24.382654+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Small-scale farming is a unique opportunity to end hunger in the Near East and North Africa</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/Small-scale-farming-is-a-unique-opportunity-to-end-hunger-in-the-Near-East-and-North-Africa-/en</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Small-scale farming is a unique opportunity to end hunger in the Near East and North Africa
+©FAO/ Experts discussing the crucial role of family farming in the eradication of poverty, hunger and all forms of malnutrition at at the NENA session organized prior the launch event of the UN's Decade of Family Farming.
+29 May 2019, Rome / Cairo - The Food and Agriculture Organization (FAO) and the International Fund for Agricultural Development (IFAD) today launched the United Nations' Decade of Family Farming and a Global Action Plan to boost support for family farmers, particularly those in developing countries. 
+Prior to the launch of the decade, FAO organized a series of events focused on aspects of family farming across different regions, as well as on challenges and opportunities for family farming. These sessions brought together representatives from a range of countries and sectors. 
+Small-scale family farming provides more than 80 percent of agricultural production and holds nearly 75 to 85 percent of agricultural lands in the Near East and North Africa region, that face numerous common challenges to achieving improved food security, nutrition and inclusive agricultural development. 
+Recent conflicts and civil instability in some countries of the region as well as rapid population growth, increasing urbanization, low growth in food production, scarce and fragile natural resources and the threat of climate change have been compounding the situation. 
+“Despite its enormous contribution to food security and to rural economy, small-scale family farming faces a number of intertwined constraints in the region impeding its productivity, profitability and contribution to economic growth,” Rachid Serraj FAO’s Senior Agricultural Officer said at the NENA session organized prior the launch event of the United Nations Decade of Family Farming. 
+"Family farming is crucial to sustainable development in many aspects, including the eradication of poverty, hunger and all forms of malnutrition, as well as in preserving natural resources, ”Serraj highlighted. 
+Serraj also emphasized on the importance the UN Decade of Family Farming and said, “It is a unique opportunity to build the resilience of smallholders and family farmers so they can prepare for and adapt to these alarming challenges.” 
+NENA Initiative on Small-Scale Family Farming
+Policy advice and best practice ideas on promoting and supporting inclusive small-scale agricultural development, is a key offering in FAO's Small-scale Family Farming Initiative launched back in 2014. 
+The initiative is developing regional programmatic work on social protection that will improve policy targeting of small holders, rural services and markets, strengthening the capacities of producers’ organizations and is piloting programmes to address youth unemployment and migration in the region. 
+In Lebanon, family farmers have limited resources and receive little to no social protection – 75 percent of small-scale farmers are not registered – causing them to implement counterproductive coping mechanisms. 
+FAO is working with the Lebanese government to strengthen the interconnections between agricultural and social policies to help rural communities and expand social protection coverage to farmers and fishers. 
+In light of this, FAO assisted the Lebanese government in establishing a digital farmers’ registry that integrates for the first time socio-economic indicators of farmers’ households and information characterizing farmers’ plots and their locations, to build information that would assist in agricultural development and provision of agricultural services as well as for designing social assistance programmes. 
+The United Nations' Decade of Family Farming
+In 2017, over 100 countries unanimously voted in the UN General Assembly to adopt the UN Decade of Family Farming 2019-2028. 
+FAO and IFAD co-lead the Decade in its global mandate to focus the efforts of the international community, including governments and the UN system, to create policies, laws and frameworks that will support family farmers to improve their food security, nutrition and incomes, thereby supporting the Sustainable Development Goals (SDGS) and investments in rural people.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:31.094534+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Lebanon Hosts the Sixth Mediterranean Forest Week</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/Lebanon-Hosts-the-Sixth-Mediterranean-Forest-Week/en</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Lebanon Hosts the Sixth Mediterranean Forest Week
+Beirut, 4 April 2019 - Under the patronage of His Excellency the Minister of Agriculture Dr. Hassan Lakiss, the the Sixth edition of the Mediterranean Forest Week (VIth MWF) held its meeting at the Grand Hills Hotel, Broumana from 1-5 April 2019 and grouped 215 participants from 30 countries representing many institutions, organizations, governmental bodies. The week covered important themes related to the Paris agreement shedding the light on the countries achievements and contributions to mitigate and adapt to climate change. Practitioners and success stories were shared with the audience, side events have showcased successful initiatives occurring in the region.
+The Participants visited the Horsh Ehden Nature Reserve, and witnessed the richness of the Cedars landscape, they were briefed on the challenges facing the nature reserve while also sharing their best practices in combating climate change effect. The participants enjoyed the beauty of the landscape and tasted local and authentic products.
+In this occasion the Food and Agriculture Organization of the UN has released a new Publication titled: “Guide to the Classical biological control of insects and pests in planted and natural forests”. A hands on practical guide for practitioners and set up systems to control forest exotic pests.
+The final day concluded with High level segment and Silva Mediterranea committee meeting to elect new bureau members.
+Held every two years, the Mediterranean Forest Week is a key platform for regional forestry related cooperation and dialogue between all relevant stakeholders. In its sixth edition, the Mediterranean Forest Week showcased forest-based solutions that are important in protecting the social, environmental, economic and cultural value of the goods and services already provided by Mediterranean forests.
+It is expected that the ‘Lebanon Declaration’ will be finalized, and confirmed during the High level segment at the closing session on Thursday 4th of April at 17:00
+17</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:37.496524+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Implementation of the 2030 Agenda for Water Efficiency, Productivity and Sustainability in NENA Countries</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/Implementation-of-the-2030-Agenda-for-Water-Efficiency-Productivity-and-Sustainability-in-NENA-Countries/en</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Implementation of the 2030 Agenda for Water Efficiency, Productivity and Sustainability in NENA Countries
+©FAOSNE participants at the conference with experts
+29 March, 2019 - Tabarka/Tunisia: As part of the 2030 Agenda for Water Efficiency and Productivity in 8 countries of the region: Morocco, Tunisia, Algeria, Egypt, Palestine, Jordan, Lebanon and Iran, FAO launched the project "Implementing the 2030 Agenda for Water Efficiency, Productivity and Sustainability in the Near East and North Africa Countries."
+The Tabarka workshop from 26 to 28 March is a continuation of activities aimed at establishing the appropriate framework for the creation of a robust water accounting system based on existing knowledge and practices as well as recent remote sensing technologies. There is also a question of defining strategies and interventions that aim to increase the biophysical and economic productivity of water used for crops.
+The main objective is to facilitate, guide and support the work of the three thematic groups: Productivity, Accounting and Nexus Water/Energy/Agriculture , which were established for the project. The expected results are the sharing of acquired knowledge on mapping soil occupation by remote sensing and the Spanish experience on water productivity. The identification and validation of pilot sites in the Jendouba and Kairouan governorates, with the finalization of the Jendouba rapid water accounting analysis and the launch of the detailed analysis of water accounting and water productivity in both sites was also covered.
+The culmination of the various consultations with national partner institutions, such as the National Institute of Field Crops (INGC), the Olive Institute and several departments involved from the Ministry of Agriculture, Water Resources and Fisheries, conducted under the coordination of the Office of Planning and Balance of Hydraulic Resources (BPEH) made it possible to identify the olive and the cereals sectors as pilot sectors for Tunisia. Various targeted groups of skilled national partners have been equipped to better control remote sensing crop mapping with field applications in Jendouba. An introductory training course on methods of rapid water accounting and concepts of water efficiency and productivity has also been carried out.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:52.133429+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FAO completes training workshops on sustainable food systems and value chains in the Near East and North Africa</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-completes-training-workshops-on-sustainable-food-systems-and-value-chains-in-the-Near-East-and-North-Africa/en</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>FAO completes training workshops on sustainable food systems and value chains in the Near East and North Africa
+©FAOSNE participants with trainers
+28 March, 2019 – Tunis/ Cairo:
+The Food and Agriculture Organization of the United Nations has successfully completed training workshops on “developing sustainable food systems and value chains in the Near East and North Africa”. The two workshops held in Cairo (10-14 March) and Tunis (25-29 March) were attended by 55 participants from FAO, government entities, research centers and other stakeholders.
+Aiming at streamlining the approach towards food systems within FAO and its partners, the 11-module training acquainted participants on the concepts related to food systems and presented tools and processes to be used on the strengthening of food systems through the sustainable food value chains development approach. The training also sensitized trainees on the importance of improving the design and implementation of integrated solutions and programs across technical disciplines.
+Funded by the Italian Agency for Cooperation and International Development, the Swedish International Development Cooperation Agency, and FAO for Small-Scale Family farming in the NENA region, , the five-day training sessions were delivered in Cairo (English) and Tunis (French), attracting participants from the whole region. They consisted of theoretical and practical sessions, including field visits to different value chains actors.
+During his inaugural speech at the latest training session in Tunisia, Ahmed Bougacha said on behalf of FAO subregional coordinator: “it is clear that there will be many significant benefits in developing sustainable food systems and value chains in countries in the region.”
+He added: “we need to address key challenges which hinder the achievement of Sustainable Development Goals in the region, including food loss and waste, unequal sharing of benefits along the food system, in addition to the double burden of obesity and malnourishment.”
+“FAO promotes the value chain approach as a practical and effective tool to address critical food system challenges that member countries face in the region.” Said Jozimo SantosRocha – Agro-Industry Officer at the FAO Office for the Near East and North Africa Region. There is a need to develop a clear framework to guide projects and the implementation of policies, and to provide greater consistency as countries and regions attempt to develop food systems holistically rather than merely focusing on isolated components.
+Each training workshop took place over the course of five days; participants of the training workshops in Cairo and Tunis included 55 participants from Algeria, Egypt, Iraq, Jordan, Lebanon, Mauritania, Morocco, Palestine, Saudi Arabia, Tunisia, United Arab Emirates, and Yemen.
+At the conclusion of the workshops, participants are enabled to replicate the training course to train targeted participants in their countries.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:44:58.847151+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sustainable water management is a key to ending hunger and poverty</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/Sustainable-water-management-is-a-key-to-ending-hunger-and-poverty/en</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sustainable water management is a key to ending hunger and poverty
+22 March 2019, Beirut – The Food and Agriculture Organization of the United Nations (FAO) actively participated in a special event organized by the United Nations Economic and Social Commission for Western Asia (ESCWA) and aimed at commemorating the World Water Day. 
+The World Water Day is held annually on the 22nd of March 2019 to advocate for the sustainable management of freshwater resources. This year’s World Water Day theme is “Leaving no one behind” as part of the 2030 Agenda for Sustainable Development. 
+During the event, FAO, ESCWA, the League of Arab States, UNESCO, Sudan, Yemen and the Lebanese Youth Parliament for water discussed the data of the recently published World Water Development Report at the regional level. 
+“The Near East and North Africa region (NENA) may be facing the most severe intensification of water scarcity in history,” Mr. Jean-Marc Faurès, FAO Regional Programme Leader for the Near East and North Africa stated during the meeting. 
+Faurès also highlighted that agriculture, which uses over 85 percent of the total freshwater, will most likely absorb the bulk of this shock and added stating, “this shortage will have major implications for food security and the rural economy of the region.” 
+In light of this, FAO, together with partners across the region is convening the “Land and Water Days 2019 for the Near East and North Africa” in Cairo during 31 March – 4 April, to find collaborative solutions for the improvement of agriculture, water management and food security in the region. 
+This upcoming conference is an unprecedented knowledge-sharing platform in NENA region that will give governments, development partners, technical experts, and civil society organizations the opportunity to jointly deliberate on innovative and effective ways to critically review prevailing patterns of agricultural production and land and water management in the region. 
+The platform will also seek new solutions to improve current patterns and evaluate their potential for sustainability and long-term change.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:05.247340+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Integrated Water Resources Management at regional level in Lebanon</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Integrated-Water-Resources-Management-at-regional-level-in-Lebanon/en</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Integrated Water Resources Management at regional level in Lebanon
+The integrated Water Resources Management project – funded by the Swiss Agency for Development and Cooperation (SDC) – is being implemented over three years (2017-2020) with a budget of 2.4 million USD. To achieve the overall impact of more effective planning and management of water resources and better water outcomes to end users in Lebanon, the project aims at providing effective means to monitor water resources in the North Lebanon Water Establishment, and enabling data sharing amongst stakeholders and informed decision transfer to end-users. Ultimately, improved monitoring will enhance the water use in the Lebanese agriculture sector and the understanding of environmental risks linked to water quality.
+Further information: maher.salman@fao.org</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:18.172445+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Lebanon celebrates World Food Day 2018</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/Lebanon-celebrates-World-Food-Day-2018/en</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lebanon celebrates World Food Day 2018
+FAO Representative in Lebanon, Dr. Maurice Saade
+16 October, 2018, Beirut - The Food and Agriculture Organization of the United Nations (FAO) and the Ministry of Agriculture in Lebanon, in collaboration with the World Food Program (WFP) celebrated World Food Day 2018, under the theme: ‘Our Actions are our Future: A #ZeroHunger world by 2030 is possible’ . The ceremony was organized at the Coral Beach Hotel in Beirut under the patronage of H.E. Minister of Agriculture, Mr. Ghazi Zeaiter.
+The official ceremony included speeches by the Minister of Agriculture, Mr. Ghazi Zeaiter, the Director General of Agriculture at the Ministry of Agriculture, Mr. Louis Lahoud, the FAO Representative in Lebanon, Dr. Maurice Saade, and the WFP Representative in Lebanon, Mr. Abdallah Al Wardat. Following the ceremony, a panel discussion focusing on Lebanese youth and their potential opportunities in the agriculture sector was held. Panel members of high profile agriculture and economic experts presented these opportunities in respect to the institution they represent and/or their area of expertise. Some 65 final year university students specializing in agriculture, as well as final year agriculture Baccalaureate Technique (BT) students attended the discussion and had the opportunity to engage in a Q&amp;A session with the panel members. The members included: economic expert and former Minister of Finance, Mr. Damianos Kattar, agriculture and development expert and former Minister, Ms. Wafa’s Dikah, Vice President and Treasurer of the Chambers of Commerce, Industry and Agriculture of Beirut and Mount Lebanon, Mr. Nabil Fahed - representing the President of the Federation of Chambers of Commerce, Industry and Agriculture in Lebanon, Mr. Mohamed Choucair, and finally representing the President of the Syndicate of Lebanese Food Industries, Mr. Ahmad Hoteit - his deputy, Mr. Mounir Al Bsat. Renowned Lebanese economic journalist, Ms. Jessy Trad, moderated the panel discussion, and a number of high profile official figures, representatives of embassies, UN agencies, civil society organizations, university deans and the media also participated in the event.
+The panel discussion was followed by two interactive exhibitions; the first included infographic displays highlighting the importance of reducing food waste, where Lebanese apples - known for their abundance in the country - were distributed along with a six recipe home cookbook titled ‘Cooking with Apples’ to encourage the use of left-over apple as an ingredient in savory dishes, and therefore contribute to the decrease in apple waste.
+The second exhibition featured FAO’s project ‘Upgrading the Technical Agriculture Education System in Lebanon’, a five year project funded by the Kingdom of the Netherlands, and implemented in collaboration with AVSI, ILO, and UNICEF. This project aims to upgrade the seven technical agriculture schools in Lebanon, while offering enrollment opportunities to young Syrian and Lebanese students. This will allow young Lebanese graduates to have a better chance in accessing the job market, and will provide young displaced Syrians in Lebanon the necessary technical qualifications and official diplomas to be able to contribute to the post-conflict reconstruction of their country. The exhibition featured 19 year old Lebanese student and beneficiary, Hadi Hamza, who started producing honey in his second technical school year, and is now selling his produce in towns nearby his village in South Lebanon. Hadi distributed samples of his honey to the event’s attendees, while other students demonstrated their work on vertical gardens. The project’s booth also included a photo exhibition with pictures dated in the 1960s of agriculture students attending the technical agriculture schools, and are now prominent figures in the agriculture sector worldwide and in Lebanon.
+The Food and Agriculture Organization of the United Nations (FAO) celebrates World Food Day on 16 October each year, the day on which the Organization was founded in 1945. This day is celebrated by more than 150 countries worldwide.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:24.939415+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FAO uses information technology for plant protection and controlling quarantine pests</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-uses-information-technology-for-plant-protection-and-controlling-quarantine-pests/en</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>FAO uses information technology for plant protection and controlling quarantine pests
+Workshop participants receiving the training.
+3 July 2018, Beirut, Lebanon – The Food and Agriculture Organization (FAO) has launched a training of trainers workshop with the participation of six member countries on the use of information technology for plant protection and controlling quarantine pests.
+During the workshop, participants from Morocco, Tunisia, Libya, Algeria, Egypt, Palestine and Lebanon focused on the “Xylella fastidiosa” bacterium – syndrome of the rapid decline of the olive tree – and specifically on the use of XylAppNENA and relative DataBase applications.
+The workshop aimed at providing training on the use of information technology for sampling and geo-localisation of the collected samples, traceability and storage of the data (sample position, operators, laboratory assay used, results of the analyses and finally a map of the sample with the result).
+This training comes under the framework of FAO’s “Preventive Measures for the Introduction and Spread of Xylella fastidiosa-Olive Quick Decline Syndrome in NENA Countries” project, which works to support governments’ efforts to reduce the risk of introduction and spread of X. fastidiosa and its harmful effects.
+The project and training workshop are in partnership with the International Centre for Advanced Mediterranean Agronomic Studies (CIHEAM).</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:31.195007+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>World Environment Day: Acting UN Special Coordinator for Lebanon Visits FAO Project Sites</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/World-Environment-Day-Acting-UN-Special-Coordinator-for-Lebanon-Visits-FAO-Project-Sites/en</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>World Environment Day: Acting UN Special Coordinator for Lebanon Visits FAO Project Sites
+On the occasion of World Environment Day, Acting United Nations Special Coordinator for Lebanon Pernille Dahler Kardel today visited the Chouf Biosphere Reserve in Mount Lebanon and examined local reforestation projects being undertaken in coordination with the UN Food and Agriculture Organization.
+“It is an inspiration to see the strong engagement of the local communities to preserve their precious natural resources and their commitment to pave the way for a more peaceful and sustainable future,” the Special Coordinator said. Reforestation efforts are improving environmental conditions in Lebanon and enabling a fuller implementation of the country’s international environmental obligations.
+Ms. Kardel planted a tree in the Maaser El-Chouf forest and visited reforestation projects in Niha, Baadaran and Masser El-Chouf that are taking place in coordination between the Ministry of Agriculture, local authorities, the Chouf Biosphere Reserve and the UN’s Food and Agriculture Organization to support the Government’s 40 million tree program that aims to increase the forest cover throughout Lebanon from the current 13 percent to 20 percent by 2030. She also visited women artisans and agro-food processors who make local products from the upper Chouf area.
+This year’s global theme for World Environment Day is “beating plastic pollution.” The Special Coordinator hoped Lebanon would join the global effort to reduce and eventually eradicate plastic pollution, including in the sea. In a statement for the occasion, the UN Secretary-General Antonio Guterres has warned that “our world is swamped by harmful plastic waste. Every year, more than 8 million tonnes end up in the oceans. Microplastics in the seas now outnumber stars in our galaxy.” He added, “On World Environment Day, the message is simple: reject single-use plastic. Refuse what you can’t re-use.”</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:37.770381+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FAO celebrates 40 years of country representations in the Near East and North Africa region</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-celebrates-40-years-of-country-representations-in-the-Near-East-and-North-Africa-region-/en</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>FAO celebrates 40 years of country representations in the Near East and North Africa region
+Opening of the photo exhibition celebrating 40 years of FAO country representation in the NENA region.
+9 May 2018, Rome – The Food and Agriculture Organization (FAO) is celebrating today the 40th anniversary of nine country representations in the Near East and North Africa (NENA) – along with the milestones and success stories it achieved in each member country.
+Between 1977 and 1979, Egypt, Iran, Iraq, Jordan, Lebanon, Mauritania, Sudan, Syria and Yemen signed agreements to establish FAO representation offices in their respective countries. This was followed by FAO-tailored support to each country based on its needs.
+On the sideline of the 34th Session of the Regional Conference for the Near East (#NERC34), Abdessalam Ould Ahmed, FAO Assistant Director General and Regional Representative for NENA, and Darine El-Khatib, Special Goodwill Ambassador for Zero Hunger for NENA, inaugurated a photo exhibition highlighting major policy- and ground-level work carried out in the nine countries.
+“The Near East and North Africa region hosted the first ever FAO regional office in Egypt, subregional office in Tunisia and country office in Lebanon; and for 40 years, fighting hunger, poverty and malnutrition have been at the heart of our work. FAO’s cooperation with member countries and support in the field are crucial in achieving the Sustainable Development Goals (SDGs) by 2030, in particular, food security and nutrition,” said Ould Ahmed during the opening of the exhibition.
+“So many of the issues FAO works on are very dear to my heart; such as nutrition, food loss and waste, water and resources waste. In addition, through its other programmes FAO is continuously supporting people displaced by conflict, strengthening livelihoods, creating youth employment and helping farmers adapt to climate change,” stated El-Khatib.
+Along the 40 years, FAO has been committed to long-term sustainable development in the region, in cooperation with host country governments. This is reflected through the Organization’s work where, for instance, Lebanon’s office remained fully active throughout the Civil War and continued to provide emergency assistance to local farmers. More recently, amid the Syrian crisis, FAO was able to launch a national animal health campaign where it vaccinated more than 11 million heads of sheep, cattle and goats against contagious diseases.
+Moving forward, FAO is committed to supporting all member countries in achieving the SDGs by 2030 to ensure not only national development, but prosperity on a regional and global level.
+View all the photo exhibition pictures here.
+Follow the hashtag #FAO40NENA</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:44.232842+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FAO and Civil Society Organizations consult on priority activities in NENA region</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-and-Civil-Society-Organizations-consult-on-priority-activities-in-NENA-region/en</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>FAO and Civil Society Organizations consult on priority activities in NENA region
+CSOs help FAO members in decision-making regarding regional priorities and action plans for food and agriculture. ©FAO/Ami Vitale
+19 February 2018, Beirut, Lebanon – In preparation for the 34th session of the Regional Conference for the Near East (NERC 34), the UN’s Food and Agriculture Organization (FAO) participated in a Consultation meeting with Civil Society Organizations (CSOs) and Non-Governmental Organizations (NGOs) that is being held in Beirut, Lebanon from 19 to 21 February 2018.
+The consultation, self-organized by CSOs’ representatives from the Near East and North Africa (NENA) region, is attended by representatives from FAO Regional Office for the NENA and FAO Representative in Lebanon.
+Discussions of the consultation focus on FAO regional priorities and the CSOs’ input in relation to the topics in the agenda of the regional conference. The consultation aims at selecting a number of CSO spokespersons to participate in NERC’s senior officers and ministerial segments in order to benefit from their analysis of the region’s challenges linked to FAO’s strategic objectives.
+FAO Representative in Lebanon, Maurice Saade, stressed during his participation, that FAO recognizes the critical role played by CSOs in the fight against hunger given their technical expertise, their proximity to and representation of the hungry and underprivileged, and their increasing presence in the field.
+“We must work at the national and regional levels, profit from the experience and expertise of CSOs and NGOs, and gain their input from the beginning in the development of policies and activity programmes,” Saade said.
+Speaking at the consultation, Kayan Jaff, FAO Senior Policy Officer for NENA highlighted that in pervious conferences, CSOs have been found to enrich the debate for FAO members decision-making regarding regional priorities and action plans.
+“FAO highly recommends that CSO spokespersons that are elected ensure a variety of representatives of farmers, indigenous peoples, fishers, women, youth, consumers, pastoralists/herders, forest dwellers, agricultural workers, and NGOs,” Jaff added.
+NERC34 will be held from 23 to 27 April 2018. It will discuss a variety of topics of high importance to the region, including climate change in semi-arid areas for sustainable agricultural development, youth employment and migration, and transboundary plant, animal and fish diseases.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:50.974112+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FAO and the Hungarian Government open Scholarship Programme to 7 NENA Countries</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/neareast/news/details/FAO-and-the-Hungarian-Government-open-Scholarship-Programme-to-7-NENA-Countries/en</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>FAO and the Hungarian Government open Scholarship Programme to 7 NENA Countries
+The Food and Agriculture Organization of the United Nations (FAO) in cooperation with the Hungarian Government has opened the scholarship programme application for the post-graduate study of agriculture.
+The two-year scholarship finances post-graduate studies in agriculture-related disciplines for promising students from developing and middle-income countries. This year, the courses offered will focus on animal husbandry, agriculture water management, and environmental engineering. The prestigious Universities of Debrecen and the Szent István will be hosting the scholarships.
+FAO’s Regional Office in the Near East and North Africa (NENA) has succeeded in expanding the programme in the region for the past years where several students from different countries have benefited from the scholarship. Currently, the programme has grown to include students from Algeria, Egypt, Jordan, Lebanon, Palestine, Sudan and Yemen.
+“This programme is a valuable opportunity for youth in the region to acquire the education and knowledge that would help them develop the food and agriculture industry in their countries. The NENA region faces many challenges and bright minds equipped with the right tools would certainly bring about considerable development,” said Nabil Gangi, FAO Deputy Regional Representative.
+The scholarship also aims at providing youth with a competitive edge in the job market while offering them a global professional network: their fellow scholars and their professors.
+Gangi added that FAO invites the ministries of agriculture as well as public and private universities in the concerned countries to disseminate the news to ensure the highest participation of eligible students and alumni.
+All expenses are covered in the programme, including application and tuition fees, basic books, dormitory accommodation, subsistence costs, and health insurance.
+The deadline for submitting applications is 28 February 2018, for the academic year starting autumn 2018.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:53.039862+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Launch of the Farmer’s Registry Pilot Phase in Lebanon</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Launch-of-the-Farmer-s-Registry-Pilot-Phase-in-Lebanon/en</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Launch of the Farmer’s Registry Pilot Phase in Lebanon
+Under the patronage of the Minister of Agriculture, H.E Mr. Ghazi Zeaiter, the Ministry of Agriculture, in collaboration with the Food and Agriculture Organization of the United Nations (FAO), launched the pilot phase for establishing a farmers’ registry in the governorates of Akkar, North Lebanon and the Bekaa from 12 till 19 November.
+The registry can be used as a basic tool for agricultural development and provision of agricultural services as well as for social assistance programmes. It aims at ensuring a starting base for an effective reach and coverage of targeted agricultural services and benefits, and potential social protection benefits/ rural services (health, crop insurance, basic income, old age pension, credits and other) to Lebanese farmers.
+Some 500 farmers participated in the pilot phase, in the presence of the Director of the FAO Regional Initiative on Small-Scale Family Farming, Alfredo Impiglia, as well as other FAO experts and advisers.
+The Minister of Agriculture, H.E Ghazi Zeaiter, and The FAO Representative in Lebanon, Maurice Saade toured the Registration Center on November 18 to examine the registration process.
+Saade was very optimistic about the success of the pilot phase, stating: "We are currently in the second phase of the farmers' registration pilot, after the first being in North Lebanon. This project has been requested by the Ministry of Agriculture, and a farmers’ registry covering all of Lebanon is planned by the Ministry at a later stage with FAO’s full support.
+In his turn, Zeaiter stated that “the process of farmers’ registration across Lebanon requires considerable efforts and financial resources. We decided to start the pilot registration phase as a first step in some villages. This is an experiment where we can estimate the costs and efforts for implementation at a national level and prepare for a comprehensive registration process. The pilot phase in North Lebanon was completed last week between November 12 and 15, and was successful. More than 200 farmers were registered in the villages of Bhannin (North Lebanon) and the villages of Bebbnine and Tel Abbas Al Gharbi in Akkar Governorate. The team at the ministry and FAO’s experts launched the pilot registration process in the province of Baalbek Hermel with the participation of farmers in the villages of Doris and Budai;” Zaiter added.
+This pilot phase will be followed by the development of a legislative framework for the establishment of a farmers' registry by project experts, to be discussed with relevant partners and institutions.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:45:58.997014+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>World Food Day 2017: Change the Future of Migration – Invest in Food Security and Rural Development</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/World-Food-Day-2017-Change-the-Future-of-Migration-Invest-in-Food-Security-and-Rural-Development/en</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>The Food and Agriculture Organization of the United Nations (FAO) and the Ministry of Agriculture in Lebanon, in collaboration with the World Food Program (WFP) and the International Organization for Migration (IOM), celebrated today World Food Day 2017, under the theme ‘Change the future of migration – Invest in food security and rural development’. The ceremony was organized at the Coral Beach Hotel in Beirut under the patronage of H.E. Minister of Agriculture, Mr. Ghazi Zeaiter.
+The ceremony was attended by the Minister of Agriculture, Mr. Ghazi Zeaiter, the FAO Representative in Lebanon, Dr. Maurice Saade, the WFP Representative in Lebanon, Mr. Dominik Heinrich, and the IOM Representative in Lebanon Mr. Fawzi Al Zioudi. A number of official figures, representatives of embassies, UN agencies, civil society organizations, universities and the media also participated in this event.
+Following the welcoming remarks by Ms. Mariam Eid, Head of the Food Industry Department at the Ministry of Agriculture, Mr. Fawzi Al Zioudi, the IOM representative in Lebanon delivered a speech in which he pointed out that “the drivers of forced migration are often associated with insufficient food security and rural poverty. Improving agriculture conditions and rural development, particularly with regard to livelihood opportunities, are thus vital to address the current migration challenges.”
+In his speech, Mr. Dominik Heinrich, WFP representative in Lebanon focused on WFP’s programs in rural areas to enhance the resilience of Lebanese communities hosting displaced Syrians after the Syrian conflict.
+Dr. Maurice Saade, FAO representative in Lebanon reiterated FAO’s strong commitment to continue to support the Ministry of Agriculture and other Lebanese institutions to achieve their shared objectives of helping Lebanese farmers and rural communities
+In his speech, the Minister of Agriculture, Mr. Ghazi Zeaiter statedthat “migration from rural to urban areas in Lebanon is a major cause of demographic and economic changes, which lead to the decline in the agricultural sector’s labor force, as well as a decline in the contribution of the agricultural sector to Lebanon’s GDP from 6% in 2004 to 4% in 2015." He concluded his statement by congratulating FAO on World Food Day.
+An innovative exhibition that showcases FAO and WFP’s work in Lebanon during 2017 was displayed at the event. The ceremony also included the distribution of Lebanese apples as a token of the role of FAO in supporting local production and Lebanese farmers.
+The Food and Agriculture Organization of the United Nations (FAO) celebrates World Food Day on 16 October each year, the day on which the Organization was founded in 1945. Each year it is celebrated by more than 150 countries worldwide.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:46:05.129175+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Towards the Enhancement of the Mediterranean Diet</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Towards-the-Enhancement-of-the-Mediterranean-Diet/en</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Towards the Enhancement of the Mediterranean Diet
+Under the patronage of H.E The Minister of Agriculture, Mr. Ghazi Zeaiter, The Food and Agriculture Organization of the United Nations (FAO), the Ministry of Agriculture in Lebanon, and the Faculty of Agriculture and Food Science at the American University of Beirut (AUB) held an inception workshop to launch the regional project: Towards the Enhancement of the Mediterranean Diet: The Case of Lebanon.
+The launch was attended by Ms. Mariam Eid representing H.E the Minister of Agriculture, The Representative of the Food and Agriculture Organization of the United Nations in Lebanon, Dr. Maurice Saade, and the Dean of the Faculty of Agriculture and Food Science at AUB, Dr. Nahla Hwalla. Guests included participants from various Lebanese Ministries, institutions, and universities, experts from FAO and AUB faculty, students and alumni.
+Mediterranean diets have been associated with reduced incidence of various chronic diseases, including coronary heart disease, mental health, and some types of cancer. They have also been identified as examples of sustainable diets. This project, funded by Italy, aims to generate evidence documenting whether and how Lebanese and Tunisian dietary consumption patterns have moved away from the traditional Mediterranean diet, in order to develop policies and interventions that guarantee a healthy diet for all. The results of this project will make an essential contribution to improve our understanding of the production, availability, access to, and consumption of foods that are part of the traditional Mediterranean diet, within a country specific context.
+Representing H.E the Minister of Agriculture, Ms. Mariam Eid assured the Minister’s commitment to the project and its objectives. She also hoped that the results of this project are capable of better informing the decisions of all key stakeholders, in both public and private sectors, including policy makers, and development specialists in the aim of ensuring higher quality nutrition to all people.
+In his turn, Dr. Maurice Saade, the FAO Representative in Lebanon expressed concern over the increase of obesity in Lebanon especially for its associated non-communicable diseases, which is due to profound societal changes such as urbanization, increased availability of prepared and processed food, as well as westernized eating habits. Dr. Saade highlighted that “FAO has been a leader in the area of defining and promoting sustainable diets, and reaffirmed “FAO’s commitment towards the eradication of hunger and the prevention of all forms of malnutrition worldwide” which makes the “protection and promotion of the Mediterranean-style diets a strategy in line with international and national strategies and priorities”.
+Dr. Nahla Hwalla, Dean of the Faculty of Agriculture and Food Science, introduced the AUB team that is collaborating with Ministry of Agriculture and FAO in conducting the project’s research. Her presentation also addressed the project deliverables in Lebanon and confirmed that the “Mediterranean diet is proven to be healthy and sustainable”.
+After a series of presentations from AUB, FAO, and the Ministry of Agriculture’s experts, an interactive discussion was held where participants shed the light on the challenges as well as the needed strategies for the successful implementation of the project.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:46:11.881665+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>National Workshop : Capacity building for food loss reduction in the Near East &amp; the Global Initiative on Food Loss and Waste Reduction</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/National-Workshop-Capacity-building-for-food-loss-reduction-in-the-Near-East-the-Global-Initiative-on-Food-Loss-and-Waste-Reduction/en</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>National Workshop : Capacity building for food loss reduction in the Near East &amp; the Global Initiative on Food Loss and Waste Reduction
+Under the patronage of H.E The Minister of Agriculture, Mr. Ghazi Zeaiter, The Food and Agriculture Organization of the United Nations (FAO) and the Ministry of Agriculture in Lebanon held a two-day National Workshop on food loss reduction on April 24 and April 25 in the Lancaster Tamar Hotel, Beirut. The workshop presentations were held by Technical National Consultants from the Lebanese University, Project Coordinators from the Ministry of Agriculture, and experts from the FAO.
+This workshop is part of an FAO Technical Cooperation Project entitled: “Capacity building for food loss reduction in the Near East” which is being implemented in Lebanon, Egypt, Iran and Jordan, where Lebanon has been focusing on the apple supply chain, under the framework of the ‘Save Food Global Initiative on Food Loss and Waste Reduction’. As part of the collaboration between FAO and the Lebanese University, Faculty of Agriculture, an assessment of apple losses at the farm level, cold storage units and marketing chain has been conducted; the social and economic aspects of the food losses in the apple supply chain in Lebanon have also been reviewed, and a training needs assessment has been conducted.
+Based on the needs assessment, the curriculum for capacity building, and training materials have been prepared and disseminated during a workshop on preventing postharvest losses in apples’ supply chain to around 30 staff members from the Ministry of Agriculture and a number of NGOs. Post-harvest food losses prevention kits have been also provided to relevant parties.
+This workshop aimed at validating the post-harvest food losses assessment in the apple supply chain by representatives of all concerned stakeholders. Participants to the capacity building training workshop trained on food safety and post-harvest, and ended the workshop with recommendations and an action plan.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:46:18.445196+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FAO-Hungary Scholarship Programme Open to Lebanon</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/FAO-Hungary-Scholarship-Programme-Open-to-Lebanon/en</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>FAO-Hungary Scholarship Programme Open to Lebanon
+Beirut 19 Jan 2017
+The Food and Agriculture Organization of the United Nations (FAO) announces that applications for the FAO-Hungary scholarship programme for the 2017-2018 Academic Year are open, and that students from Lebanon are eligible to apply for agriculture-related studies at Szent Istvan University.
+Now in its 10th year, the FAO-Hungary Master’s degree programme offers courses taught in English at the country’s renowned Szent Istvan University. These scholarships will cover the following Master of Science degree courses for the 2017-2018 Academic Year: Rural development and agribusiness; Horticulture; Agricultural water management.
+FAO Representative in Lebanon, Maurice Saade, urges students from Lebanon to apply before February 28th to benefit from the available scholarships, noting that one student from Lebanon benefitted from this scholarship in 2016-17.
+FAO will inform public and private universities in Lebanon to ensure the highest participation of eligible students and alumni.
+Interested, eligible students who are fluent in English and do not exceed 30 years of age, are invited to apply by sending the duly filled application with the necessary supporting documents to [email protected] before the end of February.
+The scholarship will cover the application and tuition fees throughout the study period, basic books and notes, dormitory accommodation, subsistence costs and healthcare.
+The courses will be attended in the following Hungarian universities:
+- Szent Istvan University, Faculty of Economics and Social Sciences
+- Szent István University, Faculty of Horticultural Science
+- Szent István University, Faculty of Agricultural and Environmental Sciences
+FAO calls upon all eligible candidates to visit the scholarship page on FAO Regional website in order to get the application form and course descriptions.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:46:20.539686+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>President Aoun Meets FAO Director-General, Welcomes Opening of Sub-Regional Office</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/President-Aoun-Meets-FAO-Director-General-Welcomes-Opening-of-Sub-Regional-Office/en</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>President Aoun Meets FAO Director-General, Welcomes Opening of Sub-Regional Office
+Lebanon aims to step up efforts to boost food security and sustainable agriculture
+14 December 2016, Beirut – Lebanese President Michel Aoun today met FAO Director-General José Graziano da Silva for talks that focused on food security and sustainable development as well as the need to provide assistance to farmers affected by the conflict in neighbouring Syria.
+President Aoun received the FAO Director-General at the presidential Baabda Palace, where Lebanon’s Agriculture Minister, Akram Chehayeb, was also present.
+The Lebanese President expressed appreciation for FAO’s decision to open a Sub-Regional office in Beirut stressing that it would receive "full support”. FAO’s Sub-Regional Office for the Mashreq countries will serve as a technical centre of excellence in support of food and nutritional security, sustainable agricultural development, as well as food safety, trade and rural development initiatives in Lebanon, Jordan, Syria, Iraq and Iran.
+Aoun stressed that sustainable development of the agriculture sector “is of major importance" for his country. The President also pointed out that he will ensure that the new government will implement "a clear strategy” for food security and agricultural development, including the conservation of Lebanon’s forest and fishery resources and the protection against animal diseases
+He also told Graziano da Silva that Lebanon was counting FAO’s assistance to provide care for displaced Syrians who have entered the country.
+For his part, Graziano da Silva briefed the president on the main activities of FAO in Lebanon, such as the support to hosting communities, the help provided to farmers affected by the crisis in Syria and capacity development and training for Lebanese people returning from Syria. FAO activities also include support for Lebanon’s National Afforestation and Reforestation Plan, upgrading of the agricultural technical education system, assistance to small farmers affected by the Syria crisis and formulation of a road map to support fisheries and aquaculture.
+Graziano Da Silva also met First Lady, Nadia Aoun, and discussed with her possible initiatives for her to champion, including campaigns of afforestation and for the protection of forest resources. The successful introduction of Quinoa in Lebanon and current efforts to distribute seeds of local varieties were also discussed.
+The FAO Director-General praised the First Lady for the special attention she has shown towards food and environment projects and stressed that FAO was ready to provide support to initiatives that fall within the Organization’s mandate.
+Minister Chehayeb praised FAO’s support to Lebanon, quoting for example, the campaign to plant 40 million trees, which is aimed at recreating Lebanon’s “green space” following a series of devastating forest fires.
+Graziano da Silva in his concluding remarks, underscored that the opening of FAO’s Sub-Regional office in Beirut would serve to address a number of agreed-upon priorities for the region, including refugees and returnees support, dealing with transboundary diseases and epidemics affecting livestock and the agricultural sector, as well as the adverse effects of climate change.
+In addition to his meeting with the President and the First Lady, Graziano da Silva also met with the outgoing Prime Minister, Tammam Salam, the Prime Minister Designate, Saad Harir, the Speaker of Parliament, Nabih Berry and with the Foreign Minister, Gebran Bassil.
+All senior officials welcomed the establishment of the new Sub-Regional office in Lebanon and expressed their full support for FAO’s work in the country and the region.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:46:22.656248+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FAO Opens New Sub-Regional Office in Lebanon to Tackle Effects of Crises</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/FAO-Opens-New-Sub-Regional-Office-in-Lebanon-to-Tackle-Effects-of-Crises-/en</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>FAO Opens New Sub-Regional Office in Lebanon to Tackle Effects of Crises
+Director-General praises countries hosting refugees, announces new programmes
+13 December 2016, Beirut
+Conflicts in Syria, Iraq and Yemen are the prime culprit behind the doubling of undernourished people in the Near East, FAO Director-General Jose Graziano da Silva said today as he visited Beirut, where FAO is opening a new sub-regional office.
+Lebanon and 14 other countries in the Near East and North Africa region achieved the Millennium Development Goal of halving hunger rates by 2015, but food security problems have grown in absolute terms due to civil conflicts in the region.
+Graziano da Silva praised the people of Lebanon and its government for “their great commitment and solidarity towards the displaced Syrians, as well as other refugees.”
+He also congratulated newly-elected President Michel Aoun and Saad Hariri, the prime minister designate.
+The country currently hosts almost 1.5 million refugees, a third of its own population, and many of them live in rural areas where public infrastructure and natural resources are both under strain.
+“The degraded food insecurity situation today in the Near East and North Africa is not only constrained by the food production index or the increased dependency on imported goods, but it is also linked to conflict, migration and the increased refugee influx,” said Akram Chehayeb, Lebanon’s Minister of Agriculture. Conflicts have a “tremendous effect” far beyond their national borders, he added.
+To address the challenge, and support countries that are taking in the lion’s share of refugees, FAO is opening its new Sub-Regional Office for the Mashreq countries. Chehayeb and Graziano da Silva signed the agreement to set up the facility at an event in Beirut today.
+The expanded office will serve as a technical centre of excellence in support of food and nutritional security, sustainable agricultural development, as well as food safety, trade and rural development initiatives in Lebanon, Jordan, Syria, Iraq and Iran. It “comes at a very crucial time as the sub-region is aggravated by longstanding challenges such as water scarcity, soil degradation, the impacts of climate change and high unemployment,” Graziano da Silva said.
+FAO scales up its presence in Lebanon
+The new sub-regional office “is not the first collaboration between FAO and Lebanon, and it will not be the last,” said Chehayeb.
+FAO is already engaged in Lebanon as part of a broader plan to boost resilience of regional communities in the face of the Syrian crisis. It has vaccinated the entire national livestock population against major transboundary animal diseases, strengthened veterinary surveillance and control systems, distributed seeds and farm tools to 20,000 people to improve homestead food production, and helped set up 500 semi-intensive poultry farms to provide food and employment.
+FAO projects to strengthen local capacity and improve water management practises are key in the long-run effort to tackle climate change, Graziano da Silva said. “Climate action offers the triple win of tackling extreme poverty, hunger and climate change at the same time,” he added.
+On Tuesday, Lebanon and FAO also signed two new major projects, both funded by the Government of the Netherlands.
+One is a three-year $8.25 million initiative to support 1,220 farmers in reclaiming degraded lands and establishing water reservoirs, as well as assisting them in establishing irrigated fruit orchards. A key element of this project is to promote agricultural livelihoods and rural jobs, with more than 80,000 days of labour expected to be required for completion.
+Another three-year $5.2 million project is geared to rehabilitating seven technical agricultural schools to give Lebanese youth and displaced persons an opportunity to acquire necessary skills to access career opportunities in farming and related agribusinesses in Lebanon and Syria.
+FAO opens new sub-regional office in Lebanon to tackle effects of crises
+Director-General praises countries hosting refugees, announces new programmes
+13 December 2016, BEIRUT--Conflicts in Syria, Iraq and Yemen are the prime culprit behind the doubling of undernourished people in the Near East, FAO Director-General José Graziano da Silva said today as he visited Beirut, where FAO is opening a new sub-regional office.
+Lebanon and 14 other countries in the Near East and North Africa region achieved the Millennium Development Goal of halving hunger rates by 2015, but food security problems have grown in absolute terms due to civil conflicts in the region.
+Graziano da Silva praised the people of Lebanon and its government for “their great commitment and solidarity towards the displaced Syrians, as well as other refugees.”
+He also congratulated newly-elected President Michel Aoun and Saad Hariri, the prime minister designate.
+The country currently hosts almost 1.5 million refugees, a third of its own population, and many of them live in rural areas where public infrastructure and natural resources are both under strain.
+“The degraded food insecurity situation today in the Near East and North Africa is not only constrained by the food production index or the increased dependency on imported goods, but it is also linked to conflict, migration and the increased refugee influx,” said Akram Chehayeb, Lebanon’s Minister of Agriculture. Conflicts have a “tremendous effect” far beyond their national borders, he added.
+To address the challenge, and support countries that are taking in the lion’s share of refugees, FAO is opening its new Sub-Regional Office for the Mashreq countries. Chehayeb and Graziano da Silva signed the agreement to set up the facility at an event in Beirut today.
+The expanded office will serve as a technical centre of excellence in support of food and nutritional security, sustainable agricultural development, as well as food safety, trade and rural development initiatives in Lebanon, Jordan, Syria, Iraq and Iran. It “comes at a very crucial time as the sub-region is aggravated by longstanding challenges such as water scarcity, soil degradation, the impacts of climate change and high unemployment,” Graziano da Silva said.
+FAO scales up its presence in Lebanon
+The new sub-regional office “is not the first collaboration between FAO and Lebanon, and it will not be the last,” said Chehayeb.
+FAO is already engaged in Lebanon as part of a broader plan to boost resilience of regional communities in the face of the Syrian crisis. It has vaccinated the entire national livestock population against major transboundary animal diseases, strengthened veterinary surveillance and control systems, distributed seeds and farm tools to 20,000 people to improve homestead food production, and helped set up 500 semi-intensive poultry farms to provide food and employment.
+FAO projects to strengthen local capacity and improve water management practises are key in the long-run effort to tackle climate change, Graziano da Silva said. “Climate action offers the triple win of tackling extreme poverty, hunger and climate change at the same time,” he added.
+On Tuesday, Lebanon and FAO also signed two new major projects, both funded by the Government of the Netherlands.
+One is a three-year $8.25 million initiative to support 1,220 farmers in reclaiming degraded lands and establishing water reservoirs, as well as assisting them in establishing irrigated fruit orchards. A key element of this project is to promote agricultural livelihoods and rural jobs, with more than 80,000 days of labour expected to be required for completion.
+Another three-year $5.2 million project is geared to rehabilitating seven technical agricultural schools to give Lebanese youth and displaced persons an opportunity to acquire necessary skills to access career opportunities in farming and related agribusinesses in Lebanon and Syria.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:46:29.136656+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>National Center for Forest Seeds of Lebanon</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/National-Center-for-Forest-Seeds-of-Lebanon/en</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>National Center for Forest Seeds of Lebanon
+Beirut – 24 November, 2016
+The Food and Agriculture Organization of the United Nations (FAO) and the Ministry of Agriculture in Lebanon have launched their project ‘National Center for Forest Seeds of Lebanon’ during an inception workshop today at the Holiday Inn. The project is funded by the State of Norway with an estimated budget of US $ 373,032 for two years. The workshop was attended by the Ambassador of Norway, H.E Ms. Lene Lind, the Director of Rural Development and Natural Resources in the Ministry of Agriculture, Dr. Chadi Mohanna, representing the Minister of Agriculture, Mr. Akram Chehayeb, the President-Director General of the Lebanese Agriculture Research Institute (LARI), Dr. Michel Afram, the FAO representative In Lebanon, Dr. Maurice Saade, and a number of officials, NGOs, and university representatives.
+In his statement, the FAO representative in Lebanon, Dr. Maurice Saade said: “This project is a step, but nonetheless a cornerstone in achieving the 40 Million Trees Programme. The major outcome is to set up a seed center, in partnership with the Lebanese Agriculture Research Institute (LARI).” He added: “This seed center will ensure the quality and traceability of the seeds and their area of origin in Lebanon. Also, it will allow the storage of the seeds from the best mother trees of the country to be used in reforestation, allowing higher resilience of plants to the impact of climate extremes”. He then expressed his warm thanks to the Embassy of Norway for their trust and their belief in the forestry sector in Lebanon, and the Ministry of Agriculture and LARI for their continuous collaboration and partnership.
+In his turn, President-Director General of LARI, Dr. Michel Afram also expressed gratitude to the Embassy of Norway and elaborated on the importance of such a project in Lebanon, and the institute’s capacity in implementing it. “I look forward to the launch of the National Center of Forest Seeds next year”, he concluded.
+H.E the Norwegian Ambassador to Lebanon, Ms. Lene Lind then stated: “Forests are essential to the well-being of people, agriculture and the environment. Therefore, we are immensely pleased to partner with the Government of Lebanon to step up the efforts to secure future forests in Lebanon”. She added: “Planting of trees and forests rely on access to quality forest seeds. The National Center for Forests Seeds has been established to meet this challenge and improve Lebanon's access to such quality seeds. The Center will provide seeds for reforestation and make it easier to plant trees adapted to a changing climate and possibly harsher conditions”
+And on behalf of H.E the Minister of Agriculture, Mr. Akram Chehayeb, the Director of Rural Development and Natural Resources, Dr. Chadi Mohanna said: “Producing a healthy and strong seedling starts with a close selection of seeds free of disease and with no physiological stress. The 40 Million Tree programme needs at least three times this number in terms of good seeds. It is therefore crucial that Lebanon has its national seed center benefiting from the generosity of Norway and the technical assistance of FAO. The close collaboration of research (LARI) and forest sector managers (RDNRD) will be the key success for this center.”
+Following the official ceremony, Dr. Magda Bou Dagher of the University of St. Joseph and Jouzour Loubnan, gave a presentation on the seed cycle under the title: Seed Adventure – from Nature to Nature.
+Consequently, Dr. Joelle Breidy of LARI presented the process of seed conservation in Lebanon and an overview of the Seed Center that will be launched under the project.
+In his turn, Dr. Abdel Hamied Hamid, Senior Forestry Officer at the FAO Regional Office for the Near East, presented a technical overview of the project ‘National Center for Forest Seeds of Lebanon’.
+The project is in line with the priority of the Ministry of Agriculture to create an effective mechanism to monitor seed quality and trace its source, as well as improve its storing process and its planting and production phases. The FAO will support the Ministry of Agriculture and the Lebanese Agricultural Research Institution (LARI) in building the capacities of specialized and technical cadres, and empowering them to implement the project’s activities in all of its stages. This is in addition to the transfer of necessary knowledge and important technological techniques to the Ministry of Agriculture through study tours to Norway, in order to ensure that national expertise is continuously and effectively managing the center after the end of the project.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:46:35.493617+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Smart Adaptation of Forest Landscapes in Mountain Areas</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/lebanon/news/detail/Smart-Adaptation-of-Forest-Landscapes-in-Mountain-Areas/en</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Smart Adaptation of Forest Landscapes in Mountain Areas
+Beirut – 10 November, 2016
+The Food and Agriculture Organization of the United Nations (FAO) and the Ministry of Agriculture in Lebanon have announced the signing of a new project under the title ‘Smart Adaptation of Forest Landscapes in Mountain Areas’ during a press conference in the Grand Serail.
+This project is part of a series of projects that aim to increase forest areas in Lebanon, as they have suffered from cutting, fires, urban expansion and quarries, resulting in forest losses equivalent to 35 percent of the forest cover. Further threats to mountain forest ecosystems are exacerbated by climate change. By 2040, rainfall is projected to decrease by 10-20 percent, temperatures to increase by 1-2°C and extreme weather events are expected to intensify, with drought periods projected to become 9 days longer.
+In his statement, the Minister of Agriculture, H.E Mr. Akram Chehayeb said: “According to meteorological reports, there will be no rain from now until the end of the month. If the projections are right, and consequently like last year, we will be facing another period of drought. We have also been facing severe cases of desertification on a yearly basis, which requires us to seriously work on afforestation projects.” He added: “A forest fire has erupted this Monday, and is still ongoing until today. We have been trying to resist the fire with very limited resources.”
+“Smart Adaptation of Forest Landscapes in Mountain Areas (SALMA)” is a five year project to be implemented by the Food and Agriculture Organization (FAO) in Lebanon starting December 2016, in close collaboration with the Ministry of Agriculture and the Ministry of Environment. The project is funded by the Global Environment Facility (GEF) with a budget of USD 7,147,635. It intends to enhance climate resilience of vulnerable forest ecosystems, while promoting the resilience and livelihoods of vulnerable rural communities in mountain areas through sustainable forest management of 1000 hectares, and the reforestation of another 1000 hectares. Interventions will also focus on reducing the risk of forest fires through the adoption of improved and innovative integrated management practices, as well as reducing the risk of pest outbreaks by promoting integrated forest management and forest restoration techniques. The project will also assist consortiums of municipalities and reforestation partners, such as NGOs and universities, to develop and implement participatory reforestation plans.
+In his opening statement, the Director of Rural and Natural Resources in the Ministry of Agriculture, Dr. Chadi Mohanna gave an overview of the National Afforestation and Reforestation Programme (NARP) also known as the 40 million trees program which was launched by the Lebanese Government in December 2012. He stressed on the importance of the SALMA project in contributing to the goal of the government to plant an additional 70,000 hectares by 2030.
+After a brief presentation of the SALMA project, the Food and Agriculture Organization Representative in Lebanon, Dr. Maurice Saade added: “that, to date, this project provides the largest financial contribution to the NARP and will allow FAO to expand its ongoing support for the implementation of the NARP, for the coordination of reforestation efforts in Lebanon and for the mobilization of additional funds for future reforestation activities in order to achieve the stated goals by 2030.”</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:46:41.925970+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
